--- a/dgx_llm_benchmark.xlsx
+++ b/dgx_llm_benchmark.xlsx
@@ -937,16 +937,16 @@
     <t xml:space="preserve">Score dispersion</t>
   </si>
   <si>
-    <t xml:space="preserve">score_stdev / score_ci95</t>
+    <t xml:space="preserve">score_stdev / score_ci95_halfwidth</t>
   </si>
   <si>
     <t xml:space="preserve">same</t>
   </si>
   <si>
-    <t xml:space="preserve">Spread across repeats. Without it a 1-point gap means nothing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repeat runs &gt;= 5.</t>
+    <t xml:space="preserve">Stdev over every graded item (not over repeats). CI uses sqrt(n_samples x repeats). At n=100 and a score near 70%, the 95% CI is about +/-9 points - two models inside that band are tied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runner computes it; grow n_samples to narrow it.</t>
   </si>
   <si>
     <t xml:space="preserve">pass@1</t>
@@ -6442,7 +6442,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
         <v>270</v>
       </c>
@@ -23790,7 +23790,7 @@
         <v>0.712</v>
       </c>
       <c r="R2" s="22" t="n">
-        <v>0.008</v>
+        <v>0.453</v>
       </c>
       <c r="S2" s="22" t="n">
         <v>0.701</v>
@@ -23824,8 +23824,8 @@
         <v>781</v>
       </c>
       <c r="AD2" s="25" t="n">
-        <f aca="false">IFERROR(1.96*R2/SQRT(K2),"")</f>
-        <v>0.00701230917743934</v>
+        <f aca="false">IFERROR(1.96*R2/SQRT(J2*K2),"")</f>
+        <v>0.0125565193775982</v>
       </c>
       <c r="AE2" s="25" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Q$2:Q$300,C$2:C$300,C2,G$2:G$300,G2,D$2:D$300,"BF16"),"")</f>
@@ -23841,7 +23841,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD3" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R3/SQRT(K3),"")</f>
+        <f aca="false">IFERROR(1.96*R3/SQRT(J3*K3),"")</f>
         <v/>
       </c>
       <c r="AE3" s="25" t="str">
@@ -23855,7 +23855,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD4" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R4/SQRT(K4),"")</f>
+        <f aca="false">IFERROR(1.96*R4/SQRT(J4*K4),"")</f>
         <v/>
       </c>
       <c r="AE4" s="25" t="str">
@@ -23869,7 +23869,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD5" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R5/SQRT(K5),"")</f>
+        <f aca="false">IFERROR(1.96*R5/SQRT(J5*K5),"")</f>
         <v/>
       </c>
       <c r="AE5" s="25" t="str">
@@ -23883,7 +23883,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD6" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R6/SQRT(K6),"")</f>
+        <f aca="false">IFERROR(1.96*R6/SQRT(J6*K6),"")</f>
         <v/>
       </c>
       <c r="AE6" s="25" t="str">
@@ -23897,7 +23897,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD7" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R7/SQRT(K7),"")</f>
+        <f aca="false">IFERROR(1.96*R7/SQRT(J7*K7),"")</f>
         <v/>
       </c>
       <c r="AE7" s="25" t="str">
@@ -23911,7 +23911,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD8" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R8/SQRT(K8),"")</f>
+        <f aca="false">IFERROR(1.96*R8/SQRT(J8*K8),"")</f>
         <v/>
       </c>
       <c r="AE8" s="25" t="str">
@@ -23925,7 +23925,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD9" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R9/SQRT(K9),"")</f>
+        <f aca="false">IFERROR(1.96*R9/SQRT(J9*K9),"")</f>
         <v/>
       </c>
       <c r="AE9" s="25" t="str">
@@ -23939,7 +23939,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD10" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R10/SQRT(K10),"")</f>
+        <f aca="false">IFERROR(1.96*R10/SQRT(J10*K10),"")</f>
         <v/>
       </c>
       <c r="AE10" s="25" t="str">
@@ -23953,7 +23953,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD11" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R11/SQRT(K11),"")</f>
+        <f aca="false">IFERROR(1.96*R11/SQRT(J11*K11),"")</f>
         <v/>
       </c>
       <c r="AE11" s="25" t="str">
@@ -23967,7 +23967,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD12" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R12/SQRT(K12),"")</f>
+        <f aca="false">IFERROR(1.96*R12/SQRT(J12*K12),"")</f>
         <v/>
       </c>
       <c r="AE12" s="25" t="str">
@@ -23981,7 +23981,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD13" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R13/SQRT(K13),"")</f>
+        <f aca="false">IFERROR(1.96*R13/SQRT(J13*K13),"")</f>
         <v/>
       </c>
       <c r="AE13" s="25" t="str">
@@ -23995,7 +23995,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD14" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R14/SQRT(K14),"")</f>
+        <f aca="false">IFERROR(1.96*R14/SQRT(J14*K14),"")</f>
         <v/>
       </c>
       <c r="AE14" s="25" t="str">
@@ -24009,7 +24009,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD15" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R15/SQRT(K15),"")</f>
+        <f aca="false">IFERROR(1.96*R15/SQRT(J15*K15),"")</f>
         <v/>
       </c>
       <c r="AE15" s="25" t="str">
@@ -24023,7 +24023,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD16" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R16/SQRT(K16),"")</f>
+        <f aca="false">IFERROR(1.96*R16/SQRT(J16*K16),"")</f>
         <v/>
       </c>
       <c r="AE16" s="25" t="str">
@@ -24037,7 +24037,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD17" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R17/SQRT(K17),"")</f>
+        <f aca="false">IFERROR(1.96*R17/SQRT(J17*K17),"")</f>
         <v/>
       </c>
       <c r="AE17" s="25" t="str">
@@ -24051,7 +24051,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD18" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R18/SQRT(K18),"")</f>
+        <f aca="false">IFERROR(1.96*R18/SQRT(J18*K18),"")</f>
         <v/>
       </c>
       <c r="AE18" s="25" t="str">
@@ -24065,7 +24065,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD19" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R19/SQRT(K19),"")</f>
+        <f aca="false">IFERROR(1.96*R19/SQRT(J19*K19),"")</f>
         <v/>
       </c>
       <c r="AE19" s="25" t="str">
@@ -24079,7 +24079,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD20" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R20/SQRT(K20),"")</f>
+        <f aca="false">IFERROR(1.96*R20/SQRT(J20*K20),"")</f>
         <v/>
       </c>
       <c r="AE20" s="25" t="str">
@@ -24093,7 +24093,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD21" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R21/SQRT(K21),"")</f>
+        <f aca="false">IFERROR(1.96*R21/SQRT(J21*K21),"")</f>
         <v/>
       </c>
       <c r="AE21" s="25" t="str">
@@ -24107,7 +24107,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD22" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R22/SQRT(K22),"")</f>
+        <f aca="false">IFERROR(1.96*R22/SQRT(J22*K22),"")</f>
         <v/>
       </c>
       <c r="AE22" s="25" t="str">
@@ -24121,7 +24121,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD23" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R23/SQRT(K23),"")</f>
+        <f aca="false">IFERROR(1.96*R23/SQRT(J23*K23),"")</f>
         <v/>
       </c>
       <c r="AE23" s="25" t="str">
@@ -24135,7 +24135,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD24" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R24/SQRT(K24),"")</f>
+        <f aca="false">IFERROR(1.96*R24/SQRT(J24*K24),"")</f>
         <v/>
       </c>
       <c r="AE24" s="25" t="str">
@@ -24149,7 +24149,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD25" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R25/SQRT(K25),"")</f>
+        <f aca="false">IFERROR(1.96*R25/SQRT(J25*K25),"")</f>
         <v/>
       </c>
       <c r="AE25" s="25" t="str">
@@ -24163,7 +24163,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD26" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R26/SQRT(K26),"")</f>
+        <f aca="false">IFERROR(1.96*R26/SQRT(J26*K26),"")</f>
         <v/>
       </c>
       <c r="AE26" s="25" t="str">
@@ -24177,7 +24177,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD27" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R27/SQRT(K27),"")</f>
+        <f aca="false">IFERROR(1.96*R27/SQRT(J27*K27),"")</f>
         <v/>
       </c>
       <c r="AE27" s="25" t="str">
@@ -24191,7 +24191,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD28" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R28/SQRT(K28),"")</f>
+        <f aca="false">IFERROR(1.96*R28/SQRT(J28*K28),"")</f>
         <v/>
       </c>
       <c r="AE28" s="25" t="str">
@@ -24205,7 +24205,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD29" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R29/SQRT(K29),"")</f>
+        <f aca="false">IFERROR(1.96*R29/SQRT(J29*K29),"")</f>
         <v/>
       </c>
       <c r="AE29" s="25" t="str">
@@ -24219,7 +24219,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD30" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R30/SQRT(K30),"")</f>
+        <f aca="false">IFERROR(1.96*R30/SQRT(J30*K30),"")</f>
         <v/>
       </c>
       <c r="AE30" s="25" t="str">
@@ -24233,7 +24233,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD31" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R31/SQRT(K31),"")</f>
+        <f aca="false">IFERROR(1.96*R31/SQRT(J31*K31),"")</f>
         <v/>
       </c>
       <c r="AE31" s="25" t="str">
@@ -24247,7 +24247,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD32" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R32/SQRT(K32),"")</f>
+        <f aca="false">IFERROR(1.96*R32/SQRT(J32*K32),"")</f>
         <v/>
       </c>
       <c r="AE32" s="25" t="str">
@@ -24261,7 +24261,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD33" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R33/SQRT(K33),"")</f>
+        <f aca="false">IFERROR(1.96*R33/SQRT(J33*K33),"")</f>
         <v/>
       </c>
       <c r="AE33" s="25" t="str">
@@ -24275,7 +24275,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD34" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R34/SQRT(K34),"")</f>
+        <f aca="false">IFERROR(1.96*R34/SQRT(J34*K34),"")</f>
         <v/>
       </c>
       <c r="AE34" s="25" t="str">
@@ -24289,7 +24289,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD35" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R35/SQRT(K35),"")</f>
+        <f aca="false">IFERROR(1.96*R35/SQRT(J35*K35),"")</f>
         <v/>
       </c>
       <c r="AE35" s="25" t="str">
@@ -24303,7 +24303,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD36" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R36/SQRT(K36),"")</f>
+        <f aca="false">IFERROR(1.96*R36/SQRT(J36*K36),"")</f>
         <v/>
       </c>
       <c r="AE36" s="25" t="str">
@@ -24317,7 +24317,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD37" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R37/SQRT(K37),"")</f>
+        <f aca="false">IFERROR(1.96*R37/SQRT(J37*K37),"")</f>
         <v/>
       </c>
       <c r="AE37" s="25" t="str">
@@ -24331,7 +24331,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD38" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R38/SQRT(K38),"")</f>
+        <f aca="false">IFERROR(1.96*R38/SQRT(J38*K38),"")</f>
         <v/>
       </c>
       <c r="AE38" s="25" t="str">
@@ -24345,7 +24345,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD39" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R39/SQRT(K39),"")</f>
+        <f aca="false">IFERROR(1.96*R39/SQRT(J39*K39),"")</f>
         <v/>
       </c>
       <c r="AE39" s="25" t="str">
@@ -24359,7 +24359,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD40" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R40/SQRT(K40),"")</f>
+        <f aca="false">IFERROR(1.96*R40/SQRT(J40*K40),"")</f>
         <v/>
       </c>
       <c r="AE40" s="25" t="str">
@@ -24373,7 +24373,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD41" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R41/SQRT(K41),"")</f>
+        <f aca="false">IFERROR(1.96*R41/SQRT(J41*K41),"")</f>
         <v/>
       </c>
       <c r="AE41" s="25" t="str">
@@ -24387,7 +24387,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD42" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R42/SQRT(K42),"")</f>
+        <f aca="false">IFERROR(1.96*R42/SQRT(J42*K42),"")</f>
         <v/>
       </c>
       <c r="AE42" s="25" t="str">
@@ -24401,7 +24401,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD43" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R43/SQRT(K43),"")</f>
+        <f aca="false">IFERROR(1.96*R43/SQRT(J43*K43),"")</f>
         <v/>
       </c>
       <c r="AE43" s="25" t="str">
@@ -24415,7 +24415,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD44" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R44/SQRT(K44),"")</f>
+        <f aca="false">IFERROR(1.96*R44/SQRT(J44*K44),"")</f>
         <v/>
       </c>
       <c r="AE44" s="25" t="str">
@@ -24429,7 +24429,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD45" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R45/SQRT(K45),"")</f>
+        <f aca="false">IFERROR(1.96*R45/SQRT(J45*K45),"")</f>
         <v/>
       </c>
       <c r="AE45" s="25" t="str">
@@ -24443,7 +24443,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD46" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R46/SQRT(K46),"")</f>
+        <f aca="false">IFERROR(1.96*R46/SQRT(J46*K46),"")</f>
         <v/>
       </c>
       <c r="AE46" s="25" t="str">
@@ -24457,7 +24457,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD47" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R47/SQRT(K47),"")</f>
+        <f aca="false">IFERROR(1.96*R47/SQRT(J47*K47),"")</f>
         <v/>
       </c>
       <c r="AE47" s="25" t="str">
@@ -24471,7 +24471,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD48" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R48/SQRT(K48),"")</f>
+        <f aca="false">IFERROR(1.96*R48/SQRT(J48*K48),"")</f>
         <v/>
       </c>
       <c r="AE48" s="25" t="str">
@@ -24485,7 +24485,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD49" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R49/SQRT(K49),"")</f>
+        <f aca="false">IFERROR(1.96*R49/SQRT(J49*K49),"")</f>
         <v/>
       </c>
       <c r="AE49" s="25" t="str">
@@ -24499,7 +24499,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD50" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R50/SQRT(K50),"")</f>
+        <f aca="false">IFERROR(1.96*R50/SQRT(J50*K50),"")</f>
         <v/>
       </c>
       <c r="AE50" s="25" t="str">
@@ -24513,7 +24513,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD51" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R51/SQRT(K51),"")</f>
+        <f aca="false">IFERROR(1.96*R51/SQRT(J51*K51),"")</f>
         <v/>
       </c>
       <c r="AE51" s="25" t="str">
@@ -24527,7 +24527,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD52" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R52/SQRT(K52),"")</f>
+        <f aca="false">IFERROR(1.96*R52/SQRT(J52*K52),"")</f>
         <v/>
       </c>
       <c r="AE52" s="25" t="str">
@@ -24541,7 +24541,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD53" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R53/SQRT(K53),"")</f>
+        <f aca="false">IFERROR(1.96*R53/SQRT(J53*K53),"")</f>
         <v/>
       </c>
       <c r="AE53" s="25" t="str">
@@ -24555,7 +24555,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD54" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R54/SQRT(K54),"")</f>
+        <f aca="false">IFERROR(1.96*R54/SQRT(J54*K54),"")</f>
         <v/>
       </c>
       <c r="AE54" s="25" t="str">
@@ -24569,7 +24569,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD55" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R55/SQRT(K55),"")</f>
+        <f aca="false">IFERROR(1.96*R55/SQRT(J55*K55),"")</f>
         <v/>
       </c>
       <c r="AE55" s="25" t="str">
@@ -24583,7 +24583,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD56" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R56/SQRT(K56),"")</f>
+        <f aca="false">IFERROR(1.96*R56/SQRT(J56*K56),"")</f>
         <v/>
       </c>
       <c r="AE56" s="25" t="str">
@@ -24597,7 +24597,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD57" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R57/SQRT(K57),"")</f>
+        <f aca="false">IFERROR(1.96*R57/SQRT(J57*K57),"")</f>
         <v/>
       </c>
       <c r="AE57" s="25" t="str">
@@ -24611,7 +24611,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD58" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R58/SQRT(K58),"")</f>
+        <f aca="false">IFERROR(1.96*R58/SQRT(J58*K58),"")</f>
         <v/>
       </c>
       <c r="AE58" s="25" t="str">
@@ -24625,7 +24625,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD59" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R59/SQRT(K59),"")</f>
+        <f aca="false">IFERROR(1.96*R59/SQRT(J59*K59),"")</f>
         <v/>
       </c>
       <c r="AE59" s="25" t="str">
@@ -24639,7 +24639,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD60" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R60/SQRT(K60),"")</f>
+        <f aca="false">IFERROR(1.96*R60/SQRT(J60*K60),"")</f>
         <v/>
       </c>
       <c r="AE60" s="25" t="str">
@@ -24653,7 +24653,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD61" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R61/SQRT(K61),"")</f>
+        <f aca="false">IFERROR(1.96*R61/SQRT(J61*K61),"")</f>
         <v/>
       </c>
       <c r="AE61" s="25" t="str">
@@ -24667,7 +24667,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD62" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R62/SQRT(K62),"")</f>
+        <f aca="false">IFERROR(1.96*R62/SQRT(J62*K62),"")</f>
         <v/>
       </c>
       <c r="AE62" s="25" t="str">
@@ -24681,7 +24681,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD63" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R63/SQRT(K63),"")</f>
+        <f aca="false">IFERROR(1.96*R63/SQRT(J63*K63),"")</f>
         <v/>
       </c>
       <c r="AE63" s="25" t="str">
@@ -24695,7 +24695,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD64" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R64/SQRT(K64),"")</f>
+        <f aca="false">IFERROR(1.96*R64/SQRT(J64*K64),"")</f>
         <v/>
       </c>
       <c r="AE64" s="25" t="str">
@@ -24709,7 +24709,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD65" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R65/SQRT(K65),"")</f>
+        <f aca="false">IFERROR(1.96*R65/SQRT(J65*K65),"")</f>
         <v/>
       </c>
       <c r="AE65" s="25" t="str">
@@ -24723,7 +24723,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD66" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R66/SQRT(K66),"")</f>
+        <f aca="false">IFERROR(1.96*R66/SQRT(J66*K66),"")</f>
         <v/>
       </c>
       <c r="AE66" s="25" t="str">
@@ -24737,7 +24737,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD67" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R67/SQRT(K67),"")</f>
+        <f aca="false">IFERROR(1.96*R67/SQRT(J67*K67),"")</f>
         <v/>
       </c>
       <c r="AE67" s="25" t="str">
@@ -24751,7 +24751,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD68" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R68/SQRT(K68),"")</f>
+        <f aca="false">IFERROR(1.96*R68/SQRT(J68*K68),"")</f>
         <v/>
       </c>
       <c r="AE68" s="25" t="str">
@@ -24765,7 +24765,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD69" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R69/SQRT(K69),"")</f>
+        <f aca="false">IFERROR(1.96*R69/SQRT(J69*K69),"")</f>
         <v/>
       </c>
       <c r="AE69" s="25" t="str">
@@ -24779,7 +24779,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD70" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R70/SQRT(K70),"")</f>
+        <f aca="false">IFERROR(1.96*R70/SQRT(J70*K70),"")</f>
         <v/>
       </c>
       <c r="AE70" s="25" t="str">
@@ -24793,7 +24793,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD71" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R71/SQRT(K71),"")</f>
+        <f aca="false">IFERROR(1.96*R71/SQRT(J71*K71),"")</f>
         <v/>
       </c>
       <c r="AE71" s="25" t="str">
@@ -24807,7 +24807,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD72" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R72/SQRT(K72),"")</f>
+        <f aca="false">IFERROR(1.96*R72/SQRT(J72*K72),"")</f>
         <v/>
       </c>
       <c r="AE72" s="25" t="str">
@@ -24821,7 +24821,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD73" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R73/SQRT(K73),"")</f>
+        <f aca="false">IFERROR(1.96*R73/SQRT(J73*K73),"")</f>
         <v/>
       </c>
       <c r="AE73" s="25" t="str">
@@ -24835,7 +24835,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD74" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R74/SQRT(K74),"")</f>
+        <f aca="false">IFERROR(1.96*R74/SQRT(J74*K74),"")</f>
         <v/>
       </c>
       <c r="AE74" s="25" t="str">
@@ -24849,7 +24849,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD75" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R75/SQRT(K75),"")</f>
+        <f aca="false">IFERROR(1.96*R75/SQRT(J75*K75),"")</f>
         <v/>
       </c>
       <c r="AE75" s="25" t="str">
@@ -24863,7 +24863,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD76" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R76/SQRT(K76),"")</f>
+        <f aca="false">IFERROR(1.96*R76/SQRT(J76*K76),"")</f>
         <v/>
       </c>
       <c r="AE76" s="25" t="str">
@@ -24877,7 +24877,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD77" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R77/SQRT(K77),"")</f>
+        <f aca="false">IFERROR(1.96*R77/SQRT(J77*K77),"")</f>
         <v/>
       </c>
       <c r="AE77" s="25" t="str">
@@ -24891,7 +24891,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD78" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R78/SQRT(K78),"")</f>
+        <f aca="false">IFERROR(1.96*R78/SQRT(J78*K78),"")</f>
         <v/>
       </c>
       <c r="AE78" s="25" t="str">
@@ -24905,7 +24905,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD79" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R79/SQRT(K79),"")</f>
+        <f aca="false">IFERROR(1.96*R79/SQRT(J79*K79),"")</f>
         <v/>
       </c>
       <c r="AE79" s="25" t="str">
@@ -24919,7 +24919,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD80" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R80/SQRT(K80),"")</f>
+        <f aca="false">IFERROR(1.96*R80/SQRT(J80*K80),"")</f>
         <v/>
       </c>
       <c r="AE80" s="25" t="str">
@@ -24933,7 +24933,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD81" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R81/SQRT(K81),"")</f>
+        <f aca="false">IFERROR(1.96*R81/SQRT(J81*K81),"")</f>
         <v/>
       </c>
       <c r="AE81" s="25" t="str">
@@ -24947,7 +24947,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD82" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R82/SQRT(K82),"")</f>
+        <f aca="false">IFERROR(1.96*R82/SQRT(J82*K82),"")</f>
         <v/>
       </c>
       <c r="AE82" s="25" t="str">
@@ -24961,7 +24961,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD83" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R83/SQRT(K83),"")</f>
+        <f aca="false">IFERROR(1.96*R83/SQRT(J83*K83),"")</f>
         <v/>
       </c>
       <c r="AE83" s="25" t="str">
@@ -24975,7 +24975,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD84" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R84/SQRT(K84),"")</f>
+        <f aca="false">IFERROR(1.96*R84/SQRT(J84*K84),"")</f>
         <v/>
       </c>
       <c r="AE84" s="25" t="str">
@@ -24989,7 +24989,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD85" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R85/SQRT(K85),"")</f>
+        <f aca="false">IFERROR(1.96*R85/SQRT(J85*K85),"")</f>
         <v/>
       </c>
       <c r="AE85" s="25" t="str">
@@ -25003,7 +25003,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD86" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R86/SQRT(K86),"")</f>
+        <f aca="false">IFERROR(1.96*R86/SQRT(J86*K86),"")</f>
         <v/>
       </c>
       <c r="AE86" s="25" t="str">
@@ -25017,7 +25017,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD87" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R87/SQRT(K87),"")</f>
+        <f aca="false">IFERROR(1.96*R87/SQRT(J87*K87),"")</f>
         <v/>
       </c>
       <c r="AE87" s="25" t="str">
@@ -25031,7 +25031,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD88" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R88/SQRT(K88),"")</f>
+        <f aca="false">IFERROR(1.96*R88/SQRT(J88*K88),"")</f>
         <v/>
       </c>
       <c r="AE88" s="25" t="str">
@@ -25045,7 +25045,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD89" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R89/SQRT(K89),"")</f>
+        <f aca="false">IFERROR(1.96*R89/SQRT(J89*K89),"")</f>
         <v/>
       </c>
       <c r="AE89" s="25" t="str">
@@ -25059,7 +25059,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD90" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R90/SQRT(K90),"")</f>
+        <f aca="false">IFERROR(1.96*R90/SQRT(J90*K90),"")</f>
         <v/>
       </c>
       <c r="AE90" s="25" t="str">
@@ -25073,7 +25073,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD91" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R91/SQRT(K91),"")</f>
+        <f aca="false">IFERROR(1.96*R91/SQRT(J91*K91),"")</f>
         <v/>
       </c>
       <c r="AE91" s="25" t="str">
@@ -25087,7 +25087,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD92" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R92/SQRT(K92),"")</f>
+        <f aca="false">IFERROR(1.96*R92/SQRT(J92*K92),"")</f>
         <v/>
       </c>
       <c r="AE92" s="25" t="str">
@@ -25101,7 +25101,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD93" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R93/SQRT(K93),"")</f>
+        <f aca="false">IFERROR(1.96*R93/SQRT(J93*K93),"")</f>
         <v/>
       </c>
       <c r="AE93" s="25" t="str">
@@ -25115,7 +25115,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD94" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R94/SQRT(K94),"")</f>
+        <f aca="false">IFERROR(1.96*R94/SQRT(J94*K94),"")</f>
         <v/>
       </c>
       <c r="AE94" s="25" t="str">
@@ -25129,7 +25129,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD95" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R95/SQRT(K95),"")</f>
+        <f aca="false">IFERROR(1.96*R95/SQRT(J95*K95),"")</f>
         <v/>
       </c>
       <c r="AE95" s="25" t="str">
@@ -25143,7 +25143,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD96" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R96/SQRT(K96),"")</f>
+        <f aca="false">IFERROR(1.96*R96/SQRT(J96*K96),"")</f>
         <v/>
       </c>
       <c r="AE96" s="25" t="str">
@@ -25157,7 +25157,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD97" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R97/SQRT(K97),"")</f>
+        <f aca="false">IFERROR(1.96*R97/SQRT(J97*K97),"")</f>
         <v/>
       </c>
       <c r="AE97" s="25" t="str">
@@ -25171,7 +25171,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD98" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R98/SQRT(K98),"")</f>
+        <f aca="false">IFERROR(1.96*R98/SQRT(J98*K98),"")</f>
         <v/>
       </c>
       <c r="AE98" s="25" t="str">
@@ -25185,7 +25185,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD99" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R99/SQRT(K99),"")</f>
+        <f aca="false">IFERROR(1.96*R99/SQRT(J99*K99),"")</f>
         <v/>
       </c>
       <c r="AE99" s="25" t="str">
@@ -25199,7 +25199,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD100" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R100/SQRT(K100),"")</f>
+        <f aca="false">IFERROR(1.96*R100/SQRT(J100*K100),"")</f>
         <v/>
       </c>
       <c r="AE100" s="25" t="str">
@@ -25213,7 +25213,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD101" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R101/SQRT(K101),"")</f>
+        <f aca="false">IFERROR(1.96*R101/SQRT(J101*K101),"")</f>
         <v/>
       </c>
       <c r="AE101" s="25" t="str">
@@ -25227,7 +25227,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD102" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R102/SQRT(K102),"")</f>
+        <f aca="false">IFERROR(1.96*R102/SQRT(J102*K102),"")</f>
         <v/>
       </c>
       <c r="AE102" s="25" t="str">
@@ -25241,7 +25241,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD103" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R103/SQRT(K103),"")</f>
+        <f aca="false">IFERROR(1.96*R103/SQRT(J103*K103),"")</f>
         <v/>
       </c>
       <c r="AE103" s="25" t="str">
@@ -25255,7 +25255,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD104" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R104/SQRT(K104),"")</f>
+        <f aca="false">IFERROR(1.96*R104/SQRT(J104*K104),"")</f>
         <v/>
       </c>
       <c r="AE104" s="25" t="str">
@@ -25269,7 +25269,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD105" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R105/SQRT(K105),"")</f>
+        <f aca="false">IFERROR(1.96*R105/SQRT(J105*K105),"")</f>
         <v/>
       </c>
       <c r="AE105" s="25" t="str">
@@ -25283,7 +25283,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD106" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R106/SQRT(K106),"")</f>
+        <f aca="false">IFERROR(1.96*R106/SQRT(J106*K106),"")</f>
         <v/>
       </c>
       <c r="AE106" s="25" t="str">
@@ -25297,7 +25297,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD107" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R107/SQRT(K107),"")</f>
+        <f aca="false">IFERROR(1.96*R107/SQRT(J107*K107),"")</f>
         <v/>
       </c>
       <c r="AE107" s="25" t="str">
@@ -25311,7 +25311,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD108" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R108/SQRT(K108),"")</f>
+        <f aca="false">IFERROR(1.96*R108/SQRT(J108*K108),"")</f>
         <v/>
       </c>
       <c r="AE108" s="25" t="str">
@@ -25325,7 +25325,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD109" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R109/SQRT(K109),"")</f>
+        <f aca="false">IFERROR(1.96*R109/SQRT(J109*K109),"")</f>
         <v/>
       </c>
       <c r="AE109" s="25" t="str">
@@ -25339,7 +25339,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD110" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R110/SQRT(K110),"")</f>
+        <f aca="false">IFERROR(1.96*R110/SQRT(J110*K110),"")</f>
         <v/>
       </c>
       <c r="AE110" s="25" t="str">
@@ -25353,7 +25353,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD111" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R111/SQRT(K111),"")</f>
+        <f aca="false">IFERROR(1.96*R111/SQRT(J111*K111),"")</f>
         <v/>
       </c>
       <c r="AE111" s="25" t="str">
@@ -25367,7 +25367,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD112" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R112/SQRT(K112),"")</f>
+        <f aca="false">IFERROR(1.96*R112/SQRT(J112*K112),"")</f>
         <v/>
       </c>
       <c r="AE112" s="25" t="str">
@@ -25381,7 +25381,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD113" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R113/SQRT(K113),"")</f>
+        <f aca="false">IFERROR(1.96*R113/SQRT(J113*K113),"")</f>
         <v/>
       </c>
       <c r="AE113" s="25" t="str">
@@ -25395,7 +25395,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD114" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R114/SQRT(K114),"")</f>
+        <f aca="false">IFERROR(1.96*R114/SQRT(J114*K114),"")</f>
         <v/>
       </c>
       <c r="AE114" s="25" t="str">
@@ -25409,7 +25409,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD115" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R115/SQRT(K115),"")</f>
+        <f aca="false">IFERROR(1.96*R115/SQRT(J115*K115),"")</f>
         <v/>
       </c>
       <c r="AE115" s="25" t="str">
@@ -25423,7 +25423,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD116" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R116/SQRT(K116),"")</f>
+        <f aca="false">IFERROR(1.96*R116/SQRT(J116*K116),"")</f>
         <v/>
       </c>
       <c r="AE116" s="25" t="str">
@@ -25437,7 +25437,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD117" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R117/SQRT(K117),"")</f>
+        <f aca="false">IFERROR(1.96*R117/SQRT(J117*K117),"")</f>
         <v/>
       </c>
       <c r="AE117" s="25" t="str">
@@ -25451,7 +25451,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD118" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R118/SQRT(K118),"")</f>
+        <f aca="false">IFERROR(1.96*R118/SQRT(J118*K118),"")</f>
         <v/>
       </c>
       <c r="AE118" s="25" t="str">
@@ -25465,7 +25465,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD119" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R119/SQRT(K119),"")</f>
+        <f aca="false">IFERROR(1.96*R119/SQRT(J119*K119),"")</f>
         <v/>
       </c>
       <c r="AE119" s="25" t="str">
@@ -25479,7 +25479,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD120" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R120/SQRT(K120),"")</f>
+        <f aca="false">IFERROR(1.96*R120/SQRT(J120*K120),"")</f>
         <v/>
       </c>
       <c r="AE120" s="25" t="str">
@@ -25493,7 +25493,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD121" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R121/SQRT(K121),"")</f>
+        <f aca="false">IFERROR(1.96*R121/SQRT(J121*K121),"")</f>
         <v/>
       </c>
       <c r="AE121" s="25" t="str">
@@ -25507,7 +25507,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD122" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R122/SQRT(K122),"")</f>
+        <f aca="false">IFERROR(1.96*R122/SQRT(J122*K122),"")</f>
         <v/>
       </c>
       <c r="AE122" s="25" t="str">
@@ -25521,7 +25521,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD123" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R123/SQRT(K123),"")</f>
+        <f aca="false">IFERROR(1.96*R123/SQRT(J123*K123),"")</f>
         <v/>
       </c>
       <c r="AE123" s="25" t="str">
@@ -25535,7 +25535,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD124" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R124/SQRT(K124),"")</f>
+        <f aca="false">IFERROR(1.96*R124/SQRT(J124*K124),"")</f>
         <v/>
       </c>
       <c r="AE124" s="25" t="str">
@@ -25549,7 +25549,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD125" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R125/SQRT(K125),"")</f>
+        <f aca="false">IFERROR(1.96*R125/SQRT(J125*K125),"")</f>
         <v/>
       </c>
       <c r="AE125" s="25" t="str">
@@ -25563,7 +25563,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD126" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R126/SQRT(K126),"")</f>
+        <f aca="false">IFERROR(1.96*R126/SQRT(J126*K126),"")</f>
         <v/>
       </c>
       <c r="AE126" s="25" t="str">
@@ -25577,7 +25577,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD127" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R127/SQRT(K127),"")</f>
+        <f aca="false">IFERROR(1.96*R127/SQRT(J127*K127),"")</f>
         <v/>
       </c>
       <c r="AE127" s="25" t="str">
@@ -25591,7 +25591,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD128" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R128/SQRT(K128),"")</f>
+        <f aca="false">IFERROR(1.96*R128/SQRT(J128*K128),"")</f>
         <v/>
       </c>
       <c r="AE128" s="25" t="str">
@@ -25605,7 +25605,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD129" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R129/SQRT(K129),"")</f>
+        <f aca="false">IFERROR(1.96*R129/SQRT(J129*K129),"")</f>
         <v/>
       </c>
       <c r="AE129" s="25" t="str">
@@ -25619,7 +25619,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD130" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R130/SQRT(K130),"")</f>
+        <f aca="false">IFERROR(1.96*R130/SQRT(J130*K130),"")</f>
         <v/>
       </c>
       <c r="AE130" s="25" t="str">
@@ -25633,7 +25633,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD131" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R131/SQRT(K131),"")</f>
+        <f aca="false">IFERROR(1.96*R131/SQRT(J131*K131),"")</f>
         <v/>
       </c>
       <c r="AE131" s="25" t="str">
@@ -25647,7 +25647,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD132" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R132/SQRT(K132),"")</f>
+        <f aca="false">IFERROR(1.96*R132/SQRT(J132*K132),"")</f>
         <v/>
       </c>
       <c r="AE132" s="25" t="str">
@@ -25661,7 +25661,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD133" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R133/SQRT(K133),"")</f>
+        <f aca="false">IFERROR(1.96*R133/SQRT(J133*K133),"")</f>
         <v/>
       </c>
       <c r="AE133" s="25" t="str">
@@ -25675,7 +25675,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD134" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R134/SQRT(K134),"")</f>
+        <f aca="false">IFERROR(1.96*R134/SQRT(J134*K134),"")</f>
         <v/>
       </c>
       <c r="AE134" s="25" t="str">
@@ -25689,7 +25689,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD135" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R135/SQRT(K135),"")</f>
+        <f aca="false">IFERROR(1.96*R135/SQRT(J135*K135),"")</f>
         <v/>
       </c>
       <c r="AE135" s="25" t="str">
@@ -25703,7 +25703,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD136" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R136/SQRT(K136),"")</f>
+        <f aca="false">IFERROR(1.96*R136/SQRT(J136*K136),"")</f>
         <v/>
       </c>
       <c r="AE136" s="25" t="str">
@@ -25717,7 +25717,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD137" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R137/SQRT(K137),"")</f>
+        <f aca="false">IFERROR(1.96*R137/SQRT(J137*K137),"")</f>
         <v/>
       </c>
       <c r="AE137" s="25" t="str">
@@ -25731,7 +25731,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD138" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R138/SQRT(K138),"")</f>
+        <f aca="false">IFERROR(1.96*R138/SQRT(J138*K138),"")</f>
         <v/>
       </c>
       <c r="AE138" s="25" t="str">
@@ -25745,7 +25745,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD139" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R139/SQRT(K139),"")</f>
+        <f aca="false">IFERROR(1.96*R139/SQRT(J139*K139),"")</f>
         <v/>
       </c>
       <c r="AE139" s="25" t="str">
@@ -25759,7 +25759,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD140" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R140/SQRT(K140),"")</f>
+        <f aca="false">IFERROR(1.96*R140/SQRT(J140*K140),"")</f>
         <v/>
       </c>
       <c r="AE140" s="25" t="str">
@@ -25773,7 +25773,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD141" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R141/SQRT(K141),"")</f>
+        <f aca="false">IFERROR(1.96*R141/SQRT(J141*K141),"")</f>
         <v/>
       </c>
       <c r="AE141" s="25" t="str">
@@ -25787,7 +25787,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD142" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R142/SQRT(K142),"")</f>
+        <f aca="false">IFERROR(1.96*R142/SQRT(J142*K142),"")</f>
         <v/>
       </c>
       <c r="AE142" s="25" t="str">
@@ -25801,7 +25801,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD143" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R143/SQRT(K143),"")</f>
+        <f aca="false">IFERROR(1.96*R143/SQRT(J143*K143),"")</f>
         <v/>
       </c>
       <c r="AE143" s="25" t="str">
@@ -25815,7 +25815,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD144" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R144/SQRT(K144),"")</f>
+        <f aca="false">IFERROR(1.96*R144/SQRT(J144*K144),"")</f>
         <v/>
       </c>
       <c r="AE144" s="25" t="str">
@@ -25829,7 +25829,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD145" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R145/SQRT(K145),"")</f>
+        <f aca="false">IFERROR(1.96*R145/SQRT(J145*K145),"")</f>
         <v/>
       </c>
       <c r="AE145" s="25" t="str">
@@ -25843,7 +25843,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD146" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R146/SQRT(K146),"")</f>
+        <f aca="false">IFERROR(1.96*R146/SQRT(J146*K146),"")</f>
         <v/>
       </c>
       <c r="AE146" s="25" t="str">
@@ -25857,7 +25857,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD147" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R147/SQRT(K147),"")</f>
+        <f aca="false">IFERROR(1.96*R147/SQRT(J147*K147),"")</f>
         <v/>
       </c>
       <c r="AE147" s="25" t="str">
@@ -25871,7 +25871,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD148" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R148/SQRT(K148),"")</f>
+        <f aca="false">IFERROR(1.96*R148/SQRT(J148*K148),"")</f>
         <v/>
       </c>
       <c r="AE148" s="25" t="str">
@@ -25885,7 +25885,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD149" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R149/SQRT(K149),"")</f>
+        <f aca="false">IFERROR(1.96*R149/SQRT(J149*K149),"")</f>
         <v/>
       </c>
       <c r="AE149" s="25" t="str">
@@ -25899,7 +25899,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD150" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R150/SQRT(K150),"")</f>
+        <f aca="false">IFERROR(1.96*R150/SQRT(J150*K150),"")</f>
         <v/>
       </c>
       <c r="AE150" s="25" t="str">
@@ -25913,7 +25913,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD151" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R151/SQRT(K151),"")</f>
+        <f aca="false">IFERROR(1.96*R151/SQRT(J151*K151),"")</f>
         <v/>
       </c>
       <c r="AE151" s="25" t="str">
@@ -25927,7 +25927,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD152" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R152/SQRT(K152),"")</f>
+        <f aca="false">IFERROR(1.96*R152/SQRT(J152*K152),"")</f>
         <v/>
       </c>
       <c r="AE152" s="25" t="str">
@@ -25941,7 +25941,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD153" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R153/SQRT(K153),"")</f>
+        <f aca="false">IFERROR(1.96*R153/SQRT(J153*K153),"")</f>
         <v/>
       </c>
       <c r="AE153" s="25" t="str">
@@ -25955,7 +25955,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD154" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R154/SQRT(K154),"")</f>
+        <f aca="false">IFERROR(1.96*R154/SQRT(J154*K154),"")</f>
         <v/>
       </c>
       <c r="AE154" s="25" t="str">
@@ -25969,7 +25969,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD155" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R155/SQRT(K155),"")</f>
+        <f aca="false">IFERROR(1.96*R155/SQRT(J155*K155),"")</f>
         <v/>
       </c>
       <c r="AE155" s="25" t="str">
@@ -25983,7 +25983,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD156" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R156/SQRT(K156),"")</f>
+        <f aca="false">IFERROR(1.96*R156/SQRT(J156*K156),"")</f>
         <v/>
       </c>
       <c r="AE156" s="25" t="str">
@@ -25997,7 +25997,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD157" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R157/SQRT(K157),"")</f>
+        <f aca="false">IFERROR(1.96*R157/SQRT(J157*K157),"")</f>
         <v/>
       </c>
       <c r="AE157" s="25" t="str">
@@ -26011,7 +26011,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD158" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R158/SQRT(K158),"")</f>
+        <f aca="false">IFERROR(1.96*R158/SQRT(J158*K158),"")</f>
         <v/>
       </c>
       <c r="AE158" s="25" t="str">
@@ -26025,7 +26025,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD159" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R159/SQRT(K159),"")</f>
+        <f aca="false">IFERROR(1.96*R159/SQRT(J159*K159),"")</f>
         <v/>
       </c>
       <c r="AE159" s="25" t="str">
@@ -26039,7 +26039,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD160" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R160/SQRT(K160),"")</f>
+        <f aca="false">IFERROR(1.96*R160/SQRT(J160*K160),"")</f>
         <v/>
       </c>
       <c r="AE160" s="25" t="str">
@@ -26053,7 +26053,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD161" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R161/SQRT(K161),"")</f>
+        <f aca="false">IFERROR(1.96*R161/SQRT(J161*K161),"")</f>
         <v/>
       </c>
       <c r="AE161" s="25" t="str">
@@ -26067,7 +26067,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD162" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R162/SQRT(K162),"")</f>
+        <f aca="false">IFERROR(1.96*R162/SQRT(J162*K162),"")</f>
         <v/>
       </c>
       <c r="AE162" s="25" t="str">
@@ -26081,7 +26081,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD163" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R163/SQRT(K163),"")</f>
+        <f aca="false">IFERROR(1.96*R163/SQRT(J163*K163),"")</f>
         <v/>
       </c>
       <c r="AE163" s="25" t="str">
@@ -26095,7 +26095,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD164" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R164/SQRT(K164),"")</f>
+        <f aca="false">IFERROR(1.96*R164/SQRT(J164*K164),"")</f>
         <v/>
       </c>
       <c r="AE164" s="25" t="str">
@@ -26109,7 +26109,7 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD165" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R165/SQRT(K165),"")</f>
+        <f aca="false">IFERROR(1.96*R165/SQRT(J165*K165),"")</f>
         <v/>
       </c>
       <c r="AE165" s="25" t="str">
@@ -26123,7 +26123,7 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD166" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R166/SQRT(K166),"")</f>
+        <f aca="false">IFERROR(1.96*R166/SQRT(J166*K166),"")</f>
         <v/>
       </c>
       <c r="AE166" s="25" t="str">
@@ -26137,7 +26137,7 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD167" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R167/SQRT(K167),"")</f>
+        <f aca="false">IFERROR(1.96*R167/SQRT(J167*K167),"")</f>
         <v/>
       </c>
       <c r="AE167" s="25" t="str">
@@ -26151,7 +26151,7 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD168" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R168/SQRT(K168),"")</f>
+        <f aca="false">IFERROR(1.96*R168/SQRT(J168*K168),"")</f>
         <v/>
       </c>
       <c r="AE168" s="25" t="str">
@@ -26165,7 +26165,7 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD169" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R169/SQRT(K169),"")</f>
+        <f aca="false">IFERROR(1.96*R169/SQRT(J169*K169),"")</f>
         <v/>
       </c>
       <c r="AE169" s="25" t="str">
@@ -26179,7 +26179,7 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD170" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R170/SQRT(K170),"")</f>
+        <f aca="false">IFERROR(1.96*R170/SQRT(J170*K170),"")</f>
         <v/>
       </c>
       <c r="AE170" s="25" t="str">
@@ -26193,7 +26193,7 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD171" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R171/SQRT(K171),"")</f>
+        <f aca="false">IFERROR(1.96*R171/SQRT(J171*K171),"")</f>
         <v/>
       </c>
       <c r="AE171" s="25" t="str">
@@ -26207,7 +26207,7 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD172" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R172/SQRT(K172),"")</f>
+        <f aca="false">IFERROR(1.96*R172/SQRT(J172*K172),"")</f>
         <v/>
       </c>
       <c r="AE172" s="25" t="str">
@@ -26221,7 +26221,7 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD173" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R173/SQRT(K173),"")</f>
+        <f aca="false">IFERROR(1.96*R173/SQRT(J173*K173),"")</f>
         <v/>
       </c>
       <c r="AE173" s="25" t="str">
@@ -26235,7 +26235,7 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD174" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R174/SQRT(K174),"")</f>
+        <f aca="false">IFERROR(1.96*R174/SQRT(J174*K174),"")</f>
         <v/>
       </c>
       <c r="AE174" s="25" t="str">
@@ -26249,7 +26249,7 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD175" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R175/SQRT(K175),"")</f>
+        <f aca="false">IFERROR(1.96*R175/SQRT(J175*K175),"")</f>
         <v/>
       </c>
       <c r="AE175" s="25" t="str">
@@ -26263,7 +26263,7 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD176" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R176/SQRT(K176),"")</f>
+        <f aca="false">IFERROR(1.96*R176/SQRT(J176*K176),"")</f>
         <v/>
       </c>
       <c r="AE176" s="25" t="str">
@@ -26277,7 +26277,7 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD177" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R177/SQRT(K177),"")</f>
+        <f aca="false">IFERROR(1.96*R177/SQRT(J177*K177),"")</f>
         <v/>
       </c>
       <c r="AE177" s="25" t="str">
@@ -26291,7 +26291,7 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD178" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R178/SQRT(K178),"")</f>
+        <f aca="false">IFERROR(1.96*R178/SQRT(J178*K178),"")</f>
         <v/>
       </c>
       <c r="AE178" s="25" t="str">
@@ -26305,7 +26305,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD179" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R179/SQRT(K179),"")</f>
+        <f aca="false">IFERROR(1.96*R179/SQRT(J179*K179),"")</f>
         <v/>
       </c>
       <c r="AE179" s="25" t="str">
@@ -26319,7 +26319,7 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD180" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R180/SQRT(K180),"")</f>
+        <f aca="false">IFERROR(1.96*R180/SQRT(J180*K180),"")</f>
         <v/>
       </c>
       <c r="AE180" s="25" t="str">
@@ -26333,7 +26333,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD181" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R181/SQRT(K181),"")</f>
+        <f aca="false">IFERROR(1.96*R181/SQRT(J181*K181),"")</f>
         <v/>
       </c>
       <c r="AE181" s="25" t="str">
@@ -26347,7 +26347,7 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD182" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R182/SQRT(K182),"")</f>
+        <f aca="false">IFERROR(1.96*R182/SQRT(J182*K182),"")</f>
         <v/>
       </c>
       <c r="AE182" s="25" t="str">
@@ -26361,7 +26361,7 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD183" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R183/SQRT(K183),"")</f>
+        <f aca="false">IFERROR(1.96*R183/SQRT(J183*K183),"")</f>
         <v/>
       </c>
       <c r="AE183" s="25" t="str">
@@ -26375,7 +26375,7 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD184" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R184/SQRT(K184),"")</f>
+        <f aca="false">IFERROR(1.96*R184/SQRT(J184*K184),"")</f>
         <v/>
       </c>
       <c r="AE184" s="25" t="str">
@@ -26389,7 +26389,7 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD185" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R185/SQRT(K185),"")</f>
+        <f aca="false">IFERROR(1.96*R185/SQRT(J185*K185),"")</f>
         <v/>
       </c>
       <c r="AE185" s="25" t="str">
@@ -26403,7 +26403,7 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD186" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R186/SQRT(K186),"")</f>
+        <f aca="false">IFERROR(1.96*R186/SQRT(J186*K186),"")</f>
         <v/>
       </c>
       <c r="AE186" s="25" t="str">
@@ -26417,7 +26417,7 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD187" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R187/SQRT(K187),"")</f>
+        <f aca="false">IFERROR(1.96*R187/SQRT(J187*K187),"")</f>
         <v/>
       </c>
       <c r="AE187" s="25" t="str">
@@ -26431,7 +26431,7 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD188" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R188/SQRT(K188),"")</f>
+        <f aca="false">IFERROR(1.96*R188/SQRT(J188*K188),"")</f>
         <v/>
       </c>
       <c r="AE188" s="25" t="str">
@@ -26445,7 +26445,7 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD189" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R189/SQRT(K189),"")</f>
+        <f aca="false">IFERROR(1.96*R189/SQRT(J189*K189),"")</f>
         <v/>
       </c>
       <c r="AE189" s="25" t="str">
@@ -26459,7 +26459,7 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD190" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R190/SQRT(K190),"")</f>
+        <f aca="false">IFERROR(1.96*R190/SQRT(J190*K190),"")</f>
         <v/>
       </c>
       <c r="AE190" s="25" t="str">
@@ -26473,7 +26473,7 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD191" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R191/SQRT(K191),"")</f>
+        <f aca="false">IFERROR(1.96*R191/SQRT(J191*K191),"")</f>
         <v/>
       </c>
       <c r="AE191" s="25" t="str">
@@ -26487,7 +26487,7 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD192" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R192/SQRT(K192),"")</f>
+        <f aca="false">IFERROR(1.96*R192/SQRT(J192*K192),"")</f>
         <v/>
       </c>
       <c r="AE192" s="25" t="str">
@@ -26501,7 +26501,7 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD193" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R193/SQRT(K193),"")</f>
+        <f aca="false">IFERROR(1.96*R193/SQRT(J193*K193),"")</f>
         <v/>
       </c>
       <c r="AE193" s="25" t="str">
@@ -26515,7 +26515,7 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD194" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R194/SQRT(K194),"")</f>
+        <f aca="false">IFERROR(1.96*R194/SQRT(J194*K194),"")</f>
         <v/>
       </c>
       <c r="AE194" s="25" t="str">
@@ -26529,7 +26529,7 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD195" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R195/SQRT(K195),"")</f>
+        <f aca="false">IFERROR(1.96*R195/SQRT(J195*K195),"")</f>
         <v/>
       </c>
       <c r="AE195" s="25" t="str">
@@ -26543,7 +26543,7 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD196" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R196/SQRT(K196),"")</f>
+        <f aca="false">IFERROR(1.96*R196/SQRT(J196*K196),"")</f>
         <v/>
       </c>
       <c r="AE196" s="25" t="str">
@@ -26557,7 +26557,7 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD197" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R197/SQRT(K197),"")</f>
+        <f aca="false">IFERROR(1.96*R197/SQRT(J197*K197),"")</f>
         <v/>
       </c>
       <c r="AE197" s="25" t="str">
@@ -26571,7 +26571,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD198" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R198/SQRT(K198),"")</f>
+        <f aca="false">IFERROR(1.96*R198/SQRT(J198*K198),"")</f>
         <v/>
       </c>
       <c r="AE198" s="25" t="str">
@@ -26585,7 +26585,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD199" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R199/SQRT(K199),"")</f>
+        <f aca="false">IFERROR(1.96*R199/SQRT(J199*K199),"")</f>
         <v/>
       </c>
       <c r="AE199" s="25" t="str">
@@ -26599,7 +26599,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD200" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R200/SQRT(K200),"")</f>
+        <f aca="false">IFERROR(1.96*R200/SQRT(J200*K200),"")</f>
         <v/>
       </c>
       <c r="AE200" s="25" t="str">
@@ -26613,7 +26613,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD201" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R201/SQRT(K201),"")</f>
+        <f aca="false">IFERROR(1.96*R201/SQRT(J201*K201),"")</f>
         <v/>
       </c>
       <c r="AE201" s="25" t="str">
@@ -26627,7 +26627,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD202" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R202/SQRT(K202),"")</f>
+        <f aca="false">IFERROR(1.96*R202/SQRT(J202*K202),"")</f>
         <v/>
       </c>
       <c r="AE202" s="25" t="str">
@@ -26641,7 +26641,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD203" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R203/SQRT(K203),"")</f>
+        <f aca="false">IFERROR(1.96*R203/SQRT(J203*K203),"")</f>
         <v/>
       </c>
       <c r="AE203" s="25" t="str">
@@ -26655,7 +26655,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD204" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R204/SQRT(K204),"")</f>
+        <f aca="false">IFERROR(1.96*R204/SQRT(J204*K204),"")</f>
         <v/>
       </c>
       <c r="AE204" s="25" t="str">
@@ -26669,7 +26669,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD205" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R205/SQRT(K205),"")</f>
+        <f aca="false">IFERROR(1.96*R205/SQRT(J205*K205),"")</f>
         <v/>
       </c>
       <c r="AE205" s="25" t="str">
@@ -26683,7 +26683,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD206" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R206/SQRT(K206),"")</f>
+        <f aca="false">IFERROR(1.96*R206/SQRT(J206*K206),"")</f>
         <v/>
       </c>
       <c r="AE206" s="25" t="str">
@@ -26697,7 +26697,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD207" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R207/SQRT(K207),"")</f>
+        <f aca="false">IFERROR(1.96*R207/SQRT(J207*K207),"")</f>
         <v/>
       </c>
       <c r="AE207" s="25" t="str">
@@ -26711,7 +26711,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD208" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R208/SQRT(K208),"")</f>
+        <f aca="false">IFERROR(1.96*R208/SQRT(J208*K208),"")</f>
         <v/>
       </c>
       <c r="AE208" s="25" t="str">
@@ -26725,7 +26725,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD209" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R209/SQRT(K209),"")</f>
+        <f aca="false">IFERROR(1.96*R209/SQRT(J209*K209),"")</f>
         <v/>
       </c>
       <c r="AE209" s="25" t="str">
@@ -26739,7 +26739,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD210" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R210/SQRT(K210),"")</f>
+        <f aca="false">IFERROR(1.96*R210/SQRT(J210*K210),"")</f>
         <v/>
       </c>
       <c r="AE210" s="25" t="str">
@@ -26753,7 +26753,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD211" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R211/SQRT(K211),"")</f>
+        <f aca="false">IFERROR(1.96*R211/SQRT(J211*K211),"")</f>
         <v/>
       </c>
       <c r="AE211" s="25" t="str">
@@ -26767,7 +26767,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD212" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R212/SQRT(K212),"")</f>
+        <f aca="false">IFERROR(1.96*R212/SQRT(J212*K212),"")</f>
         <v/>
       </c>
       <c r="AE212" s="25" t="str">
@@ -26781,7 +26781,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD213" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R213/SQRT(K213),"")</f>
+        <f aca="false">IFERROR(1.96*R213/SQRT(J213*K213),"")</f>
         <v/>
       </c>
       <c r="AE213" s="25" t="str">
@@ -26795,7 +26795,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD214" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R214/SQRT(K214),"")</f>
+        <f aca="false">IFERROR(1.96*R214/SQRT(J214*K214),"")</f>
         <v/>
       </c>
       <c r="AE214" s="25" t="str">
@@ -26809,7 +26809,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD215" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R215/SQRT(K215),"")</f>
+        <f aca="false">IFERROR(1.96*R215/SQRT(J215*K215),"")</f>
         <v/>
       </c>
       <c r="AE215" s="25" t="str">
@@ -26823,7 +26823,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD216" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R216/SQRT(K216),"")</f>
+        <f aca="false">IFERROR(1.96*R216/SQRT(J216*K216),"")</f>
         <v/>
       </c>
       <c r="AE216" s="25" t="str">
@@ -26837,7 +26837,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD217" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R217/SQRT(K217),"")</f>
+        <f aca="false">IFERROR(1.96*R217/SQRT(J217*K217),"")</f>
         <v/>
       </c>
       <c r="AE217" s="25" t="str">
@@ -26851,7 +26851,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD218" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R218/SQRT(K218),"")</f>
+        <f aca="false">IFERROR(1.96*R218/SQRT(J218*K218),"")</f>
         <v/>
       </c>
       <c r="AE218" s="25" t="str">
@@ -26865,7 +26865,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD219" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R219/SQRT(K219),"")</f>
+        <f aca="false">IFERROR(1.96*R219/SQRT(J219*K219),"")</f>
         <v/>
       </c>
       <c r="AE219" s="25" t="str">
@@ -26879,7 +26879,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD220" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R220/SQRT(K220),"")</f>
+        <f aca="false">IFERROR(1.96*R220/SQRT(J220*K220),"")</f>
         <v/>
       </c>
       <c r="AE220" s="25" t="str">
@@ -26893,7 +26893,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD221" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R221/SQRT(K221),"")</f>
+        <f aca="false">IFERROR(1.96*R221/SQRT(J221*K221),"")</f>
         <v/>
       </c>
       <c r="AE221" s="25" t="str">
@@ -26907,7 +26907,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD222" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R222/SQRT(K222),"")</f>
+        <f aca="false">IFERROR(1.96*R222/SQRT(J222*K222),"")</f>
         <v/>
       </c>
       <c r="AE222" s="25" t="str">
@@ -26921,7 +26921,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD223" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R223/SQRT(K223),"")</f>
+        <f aca="false">IFERROR(1.96*R223/SQRT(J223*K223),"")</f>
         <v/>
       </c>
       <c r="AE223" s="25" t="str">
@@ -26935,7 +26935,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD224" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R224/SQRT(K224),"")</f>
+        <f aca="false">IFERROR(1.96*R224/SQRT(J224*K224),"")</f>
         <v/>
       </c>
       <c r="AE224" s="25" t="str">
@@ -26949,7 +26949,7 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD225" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R225/SQRT(K225),"")</f>
+        <f aca="false">IFERROR(1.96*R225/SQRT(J225*K225),"")</f>
         <v/>
       </c>
       <c r="AE225" s="25" t="str">
@@ -26963,7 +26963,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD226" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R226/SQRT(K226),"")</f>
+        <f aca="false">IFERROR(1.96*R226/SQRT(J226*K226),"")</f>
         <v/>
       </c>
       <c r="AE226" s="25" t="str">
@@ -26977,7 +26977,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD227" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R227/SQRT(K227),"")</f>
+        <f aca="false">IFERROR(1.96*R227/SQRT(J227*K227),"")</f>
         <v/>
       </c>
       <c r="AE227" s="25" t="str">
@@ -26991,7 +26991,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD228" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R228/SQRT(K228),"")</f>
+        <f aca="false">IFERROR(1.96*R228/SQRT(J228*K228),"")</f>
         <v/>
       </c>
       <c r="AE228" s="25" t="str">
@@ -27005,7 +27005,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD229" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R229/SQRT(K229),"")</f>
+        <f aca="false">IFERROR(1.96*R229/SQRT(J229*K229),"")</f>
         <v/>
       </c>
       <c r="AE229" s="25" t="str">
@@ -27019,7 +27019,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD230" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R230/SQRT(K230),"")</f>
+        <f aca="false">IFERROR(1.96*R230/SQRT(J230*K230),"")</f>
         <v/>
       </c>
       <c r="AE230" s="25" t="str">
@@ -27033,7 +27033,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD231" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R231/SQRT(K231),"")</f>
+        <f aca="false">IFERROR(1.96*R231/SQRT(J231*K231),"")</f>
         <v/>
       </c>
       <c r="AE231" s="25" t="str">
@@ -27047,7 +27047,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD232" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R232/SQRT(K232),"")</f>
+        <f aca="false">IFERROR(1.96*R232/SQRT(J232*K232),"")</f>
         <v/>
       </c>
       <c r="AE232" s="25" t="str">
@@ -27061,7 +27061,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD233" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R233/SQRT(K233),"")</f>
+        <f aca="false">IFERROR(1.96*R233/SQRT(J233*K233),"")</f>
         <v/>
       </c>
       <c r="AE233" s="25" t="str">
@@ -27075,7 +27075,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD234" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R234/SQRT(K234),"")</f>
+        <f aca="false">IFERROR(1.96*R234/SQRT(J234*K234),"")</f>
         <v/>
       </c>
       <c r="AE234" s="25" t="str">
@@ -27089,7 +27089,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD235" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R235/SQRT(K235),"")</f>
+        <f aca="false">IFERROR(1.96*R235/SQRT(J235*K235),"")</f>
         <v/>
       </c>
       <c r="AE235" s="25" t="str">
@@ -27103,7 +27103,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD236" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R236/SQRT(K236),"")</f>
+        <f aca="false">IFERROR(1.96*R236/SQRT(J236*K236),"")</f>
         <v/>
       </c>
       <c r="AE236" s="25" t="str">
@@ -27117,7 +27117,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD237" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R237/SQRT(K237),"")</f>
+        <f aca="false">IFERROR(1.96*R237/SQRT(J237*K237),"")</f>
         <v/>
       </c>
       <c r="AE237" s="25" t="str">
@@ -27131,7 +27131,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD238" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R238/SQRT(K238),"")</f>
+        <f aca="false">IFERROR(1.96*R238/SQRT(J238*K238),"")</f>
         <v/>
       </c>
       <c r="AE238" s="25" t="str">
@@ -27145,7 +27145,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD239" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R239/SQRT(K239),"")</f>
+        <f aca="false">IFERROR(1.96*R239/SQRT(J239*K239),"")</f>
         <v/>
       </c>
       <c r="AE239" s="25" t="str">
@@ -27159,7 +27159,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD240" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R240/SQRT(K240),"")</f>
+        <f aca="false">IFERROR(1.96*R240/SQRT(J240*K240),"")</f>
         <v/>
       </c>
       <c r="AE240" s="25" t="str">
@@ -27173,7 +27173,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD241" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R241/SQRT(K241),"")</f>
+        <f aca="false">IFERROR(1.96*R241/SQRT(J241*K241),"")</f>
         <v/>
       </c>
       <c r="AE241" s="25" t="str">
@@ -27187,7 +27187,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD242" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R242/SQRT(K242),"")</f>
+        <f aca="false">IFERROR(1.96*R242/SQRT(J242*K242),"")</f>
         <v/>
       </c>
       <c r="AE242" s="25" t="str">
@@ -27201,7 +27201,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD243" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R243/SQRT(K243),"")</f>
+        <f aca="false">IFERROR(1.96*R243/SQRT(J243*K243),"")</f>
         <v/>
       </c>
       <c r="AE243" s="25" t="str">
@@ -27215,7 +27215,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD244" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R244/SQRT(K244),"")</f>
+        <f aca="false">IFERROR(1.96*R244/SQRT(J244*K244),"")</f>
         <v/>
       </c>
       <c r="AE244" s="25" t="str">
@@ -27229,7 +27229,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD245" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R245/SQRT(K245),"")</f>
+        <f aca="false">IFERROR(1.96*R245/SQRT(J245*K245),"")</f>
         <v/>
       </c>
       <c r="AE245" s="25" t="str">
@@ -27243,7 +27243,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD246" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R246/SQRT(K246),"")</f>
+        <f aca="false">IFERROR(1.96*R246/SQRT(J246*K246),"")</f>
         <v/>
       </c>
       <c r="AE246" s="25" t="str">
@@ -27257,7 +27257,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD247" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R247/SQRT(K247),"")</f>
+        <f aca="false">IFERROR(1.96*R247/SQRT(J247*K247),"")</f>
         <v/>
       </c>
       <c r="AE247" s="25" t="str">
@@ -27271,7 +27271,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD248" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R248/SQRT(K248),"")</f>
+        <f aca="false">IFERROR(1.96*R248/SQRT(J248*K248),"")</f>
         <v/>
       </c>
       <c r="AE248" s="25" t="str">
@@ -27285,7 +27285,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD249" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R249/SQRT(K249),"")</f>
+        <f aca="false">IFERROR(1.96*R249/SQRT(J249*K249),"")</f>
         <v/>
       </c>
       <c r="AE249" s="25" t="str">
@@ -27299,7 +27299,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD250" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R250/SQRT(K250),"")</f>
+        <f aca="false">IFERROR(1.96*R250/SQRT(J250*K250),"")</f>
         <v/>
       </c>
       <c r="AE250" s="25" t="str">
@@ -27313,7 +27313,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD251" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R251/SQRT(K251),"")</f>
+        <f aca="false">IFERROR(1.96*R251/SQRT(J251*K251),"")</f>
         <v/>
       </c>
       <c r="AE251" s="25" t="str">
@@ -27327,7 +27327,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD252" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R252/SQRT(K252),"")</f>
+        <f aca="false">IFERROR(1.96*R252/SQRT(J252*K252),"")</f>
         <v/>
       </c>
       <c r="AE252" s="25" t="str">
@@ -27341,7 +27341,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD253" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R253/SQRT(K253),"")</f>
+        <f aca="false">IFERROR(1.96*R253/SQRT(J253*K253),"")</f>
         <v/>
       </c>
       <c r="AE253" s="25" t="str">
@@ -27355,7 +27355,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD254" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R254/SQRT(K254),"")</f>
+        <f aca="false">IFERROR(1.96*R254/SQRT(J254*K254),"")</f>
         <v/>
       </c>
       <c r="AE254" s="25" t="str">
@@ -27369,7 +27369,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD255" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R255/SQRT(K255),"")</f>
+        <f aca="false">IFERROR(1.96*R255/SQRT(J255*K255),"")</f>
         <v/>
       </c>
       <c r="AE255" s="25" t="str">
@@ -27383,7 +27383,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD256" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R256/SQRT(K256),"")</f>
+        <f aca="false">IFERROR(1.96*R256/SQRT(J256*K256),"")</f>
         <v/>
       </c>
       <c r="AE256" s="25" t="str">
@@ -27397,7 +27397,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD257" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R257/SQRT(K257),"")</f>
+        <f aca="false">IFERROR(1.96*R257/SQRT(J257*K257),"")</f>
         <v/>
       </c>
       <c r="AE257" s="25" t="str">
@@ -27411,7 +27411,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD258" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R258/SQRT(K258),"")</f>
+        <f aca="false">IFERROR(1.96*R258/SQRT(J258*K258),"")</f>
         <v/>
       </c>
       <c r="AE258" s="25" t="str">
@@ -27425,7 +27425,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD259" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R259/SQRT(K259),"")</f>
+        <f aca="false">IFERROR(1.96*R259/SQRT(J259*K259),"")</f>
         <v/>
       </c>
       <c r="AE259" s="25" t="str">
@@ -27439,7 +27439,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD260" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R260/SQRT(K260),"")</f>
+        <f aca="false">IFERROR(1.96*R260/SQRT(J260*K260),"")</f>
         <v/>
       </c>
       <c r="AE260" s="25" t="str">
@@ -27453,7 +27453,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD261" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R261/SQRT(K261),"")</f>
+        <f aca="false">IFERROR(1.96*R261/SQRT(J261*K261),"")</f>
         <v/>
       </c>
       <c r="AE261" s="25" t="str">
@@ -27467,7 +27467,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD262" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R262/SQRT(K262),"")</f>
+        <f aca="false">IFERROR(1.96*R262/SQRT(J262*K262),"")</f>
         <v/>
       </c>
       <c r="AE262" s="25" t="str">
@@ -27481,7 +27481,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD263" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R263/SQRT(K263),"")</f>
+        <f aca="false">IFERROR(1.96*R263/SQRT(J263*K263),"")</f>
         <v/>
       </c>
       <c r="AE263" s="25" t="str">
@@ -27495,7 +27495,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD264" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R264/SQRT(K264),"")</f>
+        <f aca="false">IFERROR(1.96*R264/SQRT(J264*K264),"")</f>
         <v/>
       </c>
       <c r="AE264" s="25" t="str">
@@ -27509,7 +27509,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD265" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R265/SQRT(K265),"")</f>
+        <f aca="false">IFERROR(1.96*R265/SQRT(J265*K265),"")</f>
         <v/>
       </c>
       <c r="AE265" s="25" t="str">
@@ -27523,7 +27523,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD266" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R266/SQRT(K266),"")</f>
+        <f aca="false">IFERROR(1.96*R266/SQRT(J266*K266),"")</f>
         <v/>
       </c>
       <c r="AE266" s="25" t="str">
@@ -27537,7 +27537,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD267" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R267/SQRT(K267),"")</f>
+        <f aca="false">IFERROR(1.96*R267/SQRT(J267*K267),"")</f>
         <v/>
       </c>
       <c r="AE267" s="25" t="str">
@@ -27551,7 +27551,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD268" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R268/SQRT(K268),"")</f>
+        <f aca="false">IFERROR(1.96*R268/SQRT(J268*K268),"")</f>
         <v/>
       </c>
       <c r="AE268" s="25" t="str">
@@ -27565,7 +27565,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD269" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R269/SQRT(K269),"")</f>
+        <f aca="false">IFERROR(1.96*R269/SQRT(J269*K269),"")</f>
         <v/>
       </c>
       <c r="AE269" s="25" t="str">
@@ -27579,7 +27579,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD270" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R270/SQRT(K270),"")</f>
+        <f aca="false">IFERROR(1.96*R270/SQRT(J270*K270),"")</f>
         <v/>
       </c>
       <c r="AE270" s="25" t="str">
@@ -27593,7 +27593,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD271" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R271/SQRT(K271),"")</f>
+        <f aca="false">IFERROR(1.96*R271/SQRT(J271*K271),"")</f>
         <v/>
       </c>
       <c r="AE271" s="25" t="str">
@@ -27607,7 +27607,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD272" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R272/SQRT(K272),"")</f>
+        <f aca="false">IFERROR(1.96*R272/SQRT(J272*K272),"")</f>
         <v/>
       </c>
       <c r="AE272" s="25" t="str">
@@ -27621,7 +27621,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD273" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R273/SQRT(K273),"")</f>
+        <f aca="false">IFERROR(1.96*R273/SQRT(J273*K273),"")</f>
         <v/>
       </c>
       <c r="AE273" s="25" t="str">
@@ -27635,7 +27635,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD274" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R274/SQRT(K274),"")</f>
+        <f aca="false">IFERROR(1.96*R274/SQRT(J274*K274),"")</f>
         <v/>
       </c>
       <c r="AE274" s="25" t="str">
@@ -27649,7 +27649,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD275" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R275/SQRT(K275),"")</f>
+        <f aca="false">IFERROR(1.96*R275/SQRT(J275*K275),"")</f>
         <v/>
       </c>
       <c r="AE275" s="25" t="str">
@@ -27663,7 +27663,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD276" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R276/SQRT(K276),"")</f>
+        <f aca="false">IFERROR(1.96*R276/SQRT(J276*K276),"")</f>
         <v/>
       </c>
       <c r="AE276" s="25" t="str">
@@ -27677,7 +27677,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD277" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R277/SQRT(K277),"")</f>
+        <f aca="false">IFERROR(1.96*R277/SQRT(J277*K277),"")</f>
         <v/>
       </c>
       <c r="AE277" s="25" t="str">
@@ -27691,7 +27691,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD278" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R278/SQRT(K278),"")</f>
+        <f aca="false">IFERROR(1.96*R278/SQRT(J278*K278),"")</f>
         <v/>
       </c>
       <c r="AE278" s="25" t="str">
@@ -27705,7 +27705,7 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD279" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R279/SQRT(K279),"")</f>
+        <f aca="false">IFERROR(1.96*R279/SQRT(J279*K279),"")</f>
         <v/>
       </c>
       <c r="AE279" s="25" t="str">
@@ -27719,7 +27719,7 @@
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD280" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R280/SQRT(K280),"")</f>
+        <f aca="false">IFERROR(1.96*R280/SQRT(J280*K280),"")</f>
         <v/>
       </c>
       <c r="AE280" s="25" t="str">
@@ -27733,7 +27733,7 @@
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD281" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R281/SQRT(K281),"")</f>
+        <f aca="false">IFERROR(1.96*R281/SQRT(J281*K281),"")</f>
         <v/>
       </c>
       <c r="AE281" s="25" t="str">
@@ -27747,7 +27747,7 @@
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD282" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R282/SQRT(K282),"")</f>
+        <f aca="false">IFERROR(1.96*R282/SQRT(J282*K282),"")</f>
         <v/>
       </c>
       <c r="AE282" s="25" t="str">
@@ -27761,7 +27761,7 @@
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD283" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R283/SQRT(K283),"")</f>
+        <f aca="false">IFERROR(1.96*R283/SQRT(J283*K283),"")</f>
         <v/>
       </c>
       <c r="AE283" s="25" t="str">
@@ -27775,7 +27775,7 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD284" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R284/SQRT(K284),"")</f>
+        <f aca="false">IFERROR(1.96*R284/SQRT(J284*K284),"")</f>
         <v/>
       </c>
       <c r="AE284" s="25" t="str">
@@ -27789,7 +27789,7 @@
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD285" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R285/SQRT(K285),"")</f>
+        <f aca="false">IFERROR(1.96*R285/SQRT(J285*K285),"")</f>
         <v/>
       </c>
       <c r="AE285" s="25" t="str">
@@ -27803,7 +27803,7 @@
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD286" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R286/SQRT(K286),"")</f>
+        <f aca="false">IFERROR(1.96*R286/SQRT(J286*K286),"")</f>
         <v/>
       </c>
       <c r="AE286" s="25" t="str">
@@ -27817,7 +27817,7 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD287" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R287/SQRT(K287),"")</f>
+        <f aca="false">IFERROR(1.96*R287/SQRT(J287*K287),"")</f>
         <v/>
       </c>
       <c r="AE287" s="25" t="str">
@@ -27831,7 +27831,7 @@
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD288" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R288/SQRT(K288),"")</f>
+        <f aca="false">IFERROR(1.96*R288/SQRT(J288*K288),"")</f>
         <v/>
       </c>
       <c r="AE288" s="25" t="str">
@@ -27845,7 +27845,7 @@
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD289" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R289/SQRT(K289),"")</f>
+        <f aca="false">IFERROR(1.96*R289/SQRT(J289*K289),"")</f>
         <v/>
       </c>
       <c r="AE289" s="25" t="str">
@@ -27859,7 +27859,7 @@
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD290" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R290/SQRT(K290),"")</f>
+        <f aca="false">IFERROR(1.96*R290/SQRT(J290*K290),"")</f>
         <v/>
       </c>
       <c r="AE290" s="25" t="str">
@@ -27873,7 +27873,7 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD291" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R291/SQRT(K291),"")</f>
+        <f aca="false">IFERROR(1.96*R291/SQRT(J291*K291),"")</f>
         <v/>
       </c>
       <c r="AE291" s="25" t="str">
@@ -27887,7 +27887,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD292" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R292/SQRT(K292),"")</f>
+        <f aca="false">IFERROR(1.96*R292/SQRT(J292*K292),"")</f>
         <v/>
       </c>
       <c r="AE292" s="25" t="str">
@@ -27901,7 +27901,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD293" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R293/SQRT(K293),"")</f>
+        <f aca="false">IFERROR(1.96*R293/SQRT(J293*K293),"")</f>
         <v/>
       </c>
       <c r="AE293" s="25" t="str">
@@ -27915,7 +27915,7 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD294" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R294/SQRT(K294),"")</f>
+        <f aca="false">IFERROR(1.96*R294/SQRT(J294*K294),"")</f>
         <v/>
       </c>
       <c r="AE294" s="25" t="str">
@@ -27929,7 +27929,7 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD295" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R295/SQRT(K295),"")</f>
+        <f aca="false">IFERROR(1.96*R295/SQRT(J295*K295),"")</f>
         <v/>
       </c>
       <c r="AE295" s="25" t="str">
@@ -27943,7 +27943,7 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD296" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R296/SQRT(K296),"")</f>
+        <f aca="false">IFERROR(1.96*R296/SQRT(J296*K296),"")</f>
         <v/>
       </c>
       <c r="AE296" s="25" t="str">
@@ -27957,7 +27957,7 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD297" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R297/SQRT(K297),"")</f>
+        <f aca="false">IFERROR(1.96*R297/SQRT(J297*K297),"")</f>
         <v/>
       </c>
       <c r="AE297" s="25" t="str">
@@ -27971,7 +27971,7 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD298" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R298/SQRT(K298),"")</f>
+        <f aca="false">IFERROR(1.96*R298/SQRT(J298*K298),"")</f>
         <v/>
       </c>
       <c r="AE298" s="25" t="str">
@@ -27985,7 +27985,7 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD299" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R299/SQRT(K299),"")</f>
+        <f aca="false">IFERROR(1.96*R299/SQRT(J299*K299),"")</f>
         <v/>
       </c>
       <c r="AE299" s="25" t="str">
@@ -27999,7 +27999,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AD300" s="25" t="str">
-        <f aca="false">IFERROR(1.96*R300/SQRT(K300),"")</f>
+        <f aca="false">IFERROR(1.96*R300/SQRT(J300*K300),"")</f>
         <v/>
       </c>
       <c r="AE300" s="25" t="str">

--- a/dgx_llm_benchmark.xlsx
+++ b/dgx_llm_benchmark.xlsx
@@ -20,7 +20,7 @@
     <sheet name="Summary" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Models!$A$4:$R$27</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Models!$A$4:$R$29</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Ollama_Pull_Log!$A$4:$K$404</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Parameters!$A$4:$H$78</definedName>
     <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Perf_Results!$A$1:$AZ$400</definedName>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="810">
   <si>
     <t xml:space="preserve">DGX LLM Benchmark - data collection workbook</t>
   </si>
@@ -1921,7 +1921,49 @@
     <t xml:space="preserve">nvidia/Llama-3_3-Nemotron-Super-49B-v1</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA-tuned; expect best TRT-LLM numbers</t>
+    <t xml:space="preserve">NVIDIA-tuned; expect best TRT-LLM numbers. No Ollama tag - vLLM/TRT-LLM only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nemotron-70b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llama 3.1 Nemotron 70B Instruct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA Open Model / Llama 3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nvidia/Llama-3.1-Nemotron-70B-Instruct-HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nemotron:70b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA RLHF tune of Llama 3.1 70B. Direct A/B against llama-3.3-70b on the same hardware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nemotron-mini-4b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nemotron Mini 4B Instruct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA Community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nvidia/Nemotron-Mini-4B-Instruct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nemotron-mini:4b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BF16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small-model efficiency reference; short context limits which shapes apply</t>
   </si>
   <si>
     <t xml:space="preserve">olmo-2-32b</t>
@@ -1934,12 +1976,6 @@
   </si>
   <si>
     <t xml:space="preserve">allenai/OLMo-2-0325-32B-Instruct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BF16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2</t>
   </si>
   <si>
     <t xml:space="preserve">Fully open data/training - reproducibility reference</t>
@@ -3452,7 +3488,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -3470,12 +3506,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3492,40 +3528,40 @@
         <v>524</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4191,15 +4227,15 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="str">
         <f aca="false">IF(Models!A15="","",Models!A15)</f>
-        <v>olmo-2-32b</v>
+        <v>nemotron-70b</v>
       </c>
       <c r="B15" s="29" t="str">
         <f aca="false">IF(Models!B15="","",Models!B15)</f>
-        <v>OLMo 2 32B Instruct</v>
+        <v>Llama 3.1 Nemotron 70B Instruct</v>
       </c>
       <c r="C15" s="29" t="str">
         <f aca="false">IF(Models!C15="","",Models!C15)</f>
-        <v>Allen Institute (AI2)</v>
+        <v>NVIDIA</v>
       </c>
       <c r="D15" s="29" t="str">
         <f aca="false">IF(Models!D15="","",Models!D15)</f>
@@ -4257,19 +4293,19 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="str">
         <f aca="false">IF(Models!A16="","",Models!A16)</f>
-        <v>mistral-small-3</v>
+        <v>nemotron-mini-4b</v>
       </c>
       <c r="B16" s="29" t="str">
         <f aca="false">IF(Models!B16="","",Models!B16)</f>
-        <v>Mistral Small 3.x Instruct</v>
+        <v>Nemotron Mini 4B Instruct</v>
       </c>
       <c r="C16" s="29" t="str">
         <f aca="false">IF(Models!C16="","",Models!C16)</f>
-        <v>Mistral AI</v>
+        <v>NVIDIA</v>
       </c>
       <c r="D16" s="29" t="str">
         <f aca="false">IF(Models!D16="","",Models!D16)</f>
-        <v>France</v>
+        <v>USA</v>
       </c>
       <c r="E16" s="30" t="n">
         <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A16)</f>
@@ -4323,19 +4359,19 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="str">
         <f aca="false">IF(Models!A17="","",Models!A17)</f>
-        <v>mixtral-8x22b</v>
+        <v>olmo-2-32b</v>
       </c>
       <c r="B17" s="29" t="str">
         <f aca="false">IF(Models!B17="","",Models!B17)</f>
-        <v>Mixtral 8x22B Instruct</v>
+        <v>OLMo 2 32B Instruct</v>
       </c>
       <c r="C17" s="29" t="str">
         <f aca="false">IF(Models!C17="","",Models!C17)</f>
-        <v>Mistral AI</v>
+        <v>Allen Institute (AI2)</v>
       </c>
       <c r="D17" s="29" t="str">
         <f aca="false">IF(Models!D17="","",Models!D17)</f>
-        <v>France</v>
+        <v>USA</v>
       </c>
       <c r="E17" s="30" t="n">
         <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A17)</f>
@@ -4389,19 +4425,19 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="29" t="str">
         <f aca="false">IF(Models!A18="","",Models!A18)</f>
-        <v>glm-4.5</v>
+        <v>mistral-small-3</v>
       </c>
       <c r="B18" s="29" t="str">
         <f aca="false">IF(Models!B18="","",Models!B18)</f>
-        <v>GLM-4.5</v>
+        <v>Mistral Small 3.x Instruct</v>
       </c>
       <c r="C18" s="29" t="str">
         <f aca="false">IF(Models!C18="","",Models!C18)</f>
-        <v>Zhipu AI / Z.ai</v>
+        <v>Mistral AI</v>
       </c>
       <c r="D18" s="29" t="str">
         <f aca="false">IF(Models!D18="","",Models!D18)</f>
-        <v>China</v>
+        <v>France</v>
       </c>
       <c r="E18" s="30" t="n">
         <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A18)</f>
@@ -4455,19 +4491,19 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="str">
         <f aca="false">IF(Models!A19="","",Models!A19)</f>
-        <v>kimi-k2</v>
+        <v>mixtral-8x22b</v>
       </c>
       <c r="B19" s="29" t="str">
         <f aca="false">IF(Models!B19="","",Models!B19)</f>
-        <v>Kimi K2 Instruct</v>
+        <v>Mixtral 8x22B Instruct</v>
       </c>
       <c r="C19" s="29" t="str">
         <f aca="false">IF(Models!C19="","",Models!C19)</f>
-        <v>Moonshot AI</v>
+        <v>Mistral AI</v>
       </c>
       <c r="D19" s="29" t="str">
         <f aca="false">IF(Models!D19="","",Models!D19)</f>
-        <v>China</v>
+        <v>France</v>
       </c>
       <c r="E19" s="30" t="n">
         <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A19)</f>
@@ -4521,15 +4557,15 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="str">
         <f aca="false">IF(Models!A20="","",Models!A20)</f>
-        <v>minimax-m1</v>
+        <v>glm-4.5</v>
       </c>
       <c r="B20" s="29" t="str">
         <f aca="false">IF(Models!B20="","",Models!B20)</f>
-        <v>MiniMax-M1</v>
+        <v>GLM-4.5</v>
       </c>
       <c r="C20" s="29" t="str">
         <f aca="false">IF(Models!C20="","",Models!C20)</f>
-        <v>MiniMax</v>
+        <v>Zhipu AI / Z.ai</v>
       </c>
       <c r="D20" s="29" t="str">
         <f aca="false">IF(Models!D20="","",Models!D20)</f>
@@ -4587,15 +4623,15 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="str">
         <f aca="false">IF(Models!A21="","",Models!A21)</f>
-        <v>internlm3-8b</v>
+        <v>kimi-k2</v>
       </c>
       <c r="B21" s="29" t="str">
         <f aca="false">IF(Models!B21="","",Models!B21)</f>
-        <v>InternLM3 8B Instruct</v>
+        <v>Kimi K2 Instruct</v>
       </c>
       <c r="C21" s="29" t="str">
         <f aca="false">IF(Models!C21="","",Models!C21)</f>
-        <v>Shanghai AI Lab</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="D21" s="29" t="str">
         <f aca="false">IF(Models!D21="","",Models!D21)</f>
@@ -4653,19 +4689,19 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="29" t="str">
         <f aca="false">IF(Models!A22="","",Models!A22)</f>
-        <v>aya-expanse-32b</v>
+        <v>minimax-m1</v>
       </c>
       <c r="B22" s="29" t="str">
         <f aca="false">IF(Models!B22="","",Models!B22)</f>
-        <v>Aya Expanse 32B</v>
+        <v>MiniMax-M1</v>
       </c>
       <c r="C22" s="29" t="str">
         <f aca="false">IF(Models!C22="","",Models!C22)</f>
-        <v>Cohere</v>
+        <v>MiniMax</v>
       </c>
       <c r="D22" s="29" t="str">
         <f aca="false">IF(Models!D22="","",Models!D22)</f>
-        <v>Canada</v>
+        <v>China</v>
       </c>
       <c r="E22" s="30" t="n">
         <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A22)</f>
@@ -4719,19 +4755,19 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="str">
         <f aca="false">IF(Models!A23="","",Models!A23)</f>
-        <v>falcon3-10b</v>
+        <v>internlm3-8b</v>
       </c>
       <c r="B23" s="29" t="str">
         <f aca="false">IF(Models!B23="","",Models!B23)</f>
-        <v>Falcon 3 10B Instruct</v>
+        <v>InternLM3 8B Instruct</v>
       </c>
       <c r="C23" s="29" t="str">
         <f aca="false">IF(Models!C23="","",Models!C23)</f>
-        <v>TII</v>
+        <v>Shanghai AI Lab</v>
       </c>
       <c r="D23" s="29" t="str">
         <f aca="false">IF(Models!D23="","",Models!D23)</f>
-        <v>UAE</v>
+        <v>China</v>
       </c>
       <c r="E23" s="30" t="n">
         <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A23)</f>
@@ -4785,19 +4821,19 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="str">
         <f aca="false">IF(Models!A24="","",Models!A24)</f>
-        <v>jamba-1.5-mini</v>
+        <v>aya-expanse-32b</v>
       </c>
       <c r="B24" s="29" t="str">
         <f aca="false">IF(Models!B24="","",Models!B24)</f>
-        <v>Jamba 1.5 Mini</v>
+        <v>Aya Expanse 32B</v>
       </c>
       <c r="C24" s="29" t="str">
         <f aca="false">IF(Models!C24="","",Models!C24)</f>
-        <v>AI21 Labs</v>
+        <v>Cohere</v>
       </c>
       <c r="D24" s="29" t="str">
         <f aca="false">IF(Models!D24="","",Models!D24)</f>
-        <v>Israel</v>
+        <v>Canada</v>
       </c>
       <c r="E24" s="30" t="n">
         <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A24)</f>
@@ -4851,19 +4887,19 @@
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="str">
         <f aca="false">IF(Models!A25="","",Models!A25)</f>
-        <v>exaone-4-32b</v>
+        <v>falcon3-10b</v>
       </c>
       <c r="B25" s="29" t="str">
         <f aca="false">IF(Models!B25="","",Models!B25)</f>
-        <v>EXAONE 4.0 32B</v>
+        <v>Falcon 3 10B Instruct</v>
       </c>
       <c r="C25" s="29" t="str">
         <f aca="false">IF(Models!C25="","",Models!C25)</f>
-        <v>LG AI Research</v>
+        <v>TII</v>
       </c>
       <c r="D25" s="29" t="str">
         <f aca="false">IF(Models!D25="","",Models!D25)</f>
-        <v>South Korea</v>
+        <v>UAE</v>
       </c>
       <c r="E25" s="30" t="n">
         <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A25)</f>
@@ -4917,19 +4953,19 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="str">
         <f aca="false">IF(Models!A26="","",Models!A26)</f>
-        <v>sarvam-m</v>
+        <v>jamba-1.5-mini</v>
       </c>
       <c r="B26" s="29" t="str">
         <f aca="false">IF(Models!B26="","",Models!B26)</f>
-        <v>Sarvam-M</v>
+        <v>Jamba 1.5 Mini</v>
       </c>
       <c r="C26" s="29" t="str">
         <f aca="false">IF(Models!C26="","",Models!C26)</f>
-        <v>Sarvam AI</v>
+        <v>AI21 Labs</v>
       </c>
       <c r="D26" s="29" t="str">
         <f aca="false">IF(Models!D26="","",Models!D26)</f>
-        <v>India</v>
+        <v>Israel</v>
       </c>
       <c r="E26" s="30" t="n">
         <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A26)</f>
@@ -4983,19 +5019,19 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="str">
         <f aca="false">IF(Models!A27="","",Models!A27)</f>
-        <v>sea-lion-v3</v>
+        <v>exaone-4-32b</v>
       </c>
       <c r="B27" s="29" t="str">
         <f aca="false">IF(Models!B27="","",Models!B27)</f>
-        <v>SEA-LION v3 (Gemma-based)</v>
+        <v>EXAONE 4.0 32B</v>
       </c>
       <c r="C27" s="29" t="str">
         <f aca="false">IF(Models!C27="","",Models!C27)</f>
-        <v>AI Singapore</v>
+        <v>LG AI Research</v>
       </c>
       <c r="D27" s="29" t="str">
         <f aca="false">IF(Models!D27="","",Models!D27)</f>
-        <v>Singapore</v>
+        <v>South Korea</v>
       </c>
       <c r="E27" s="30" t="n">
         <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A27)</f>
@@ -5046,9 +5082,141 @@
         <v/>
       </c>
     </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="29" t="str">
+        <f aca="false">IF(Models!A28="","",Models!A28)</f>
+        <v>sarvam-m</v>
+      </c>
+      <c r="B28" s="29" t="str">
+        <f aca="false">IF(Models!B28="","",Models!B28)</f>
+        <v>Sarvam-M</v>
+      </c>
+      <c r="C28" s="29" t="str">
+        <f aca="false">IF(Models!C28="","",Models!C28)</f>
+        <v>Sarvam AI</v>
+      </c>
+      <c r="D28" s="29" t="str">
+        <f aca="false">IF(Models!D28="","",Models!D28)</f>
+        <v>India</v>
+      </c>
+      <c r="E28" s="30" t="n">
+        <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A28)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="20" t="str">
+        <f aca="false">IF($E28=0,"",IFERROR(_xlfn.MAXIFS(Perf_Results!$AI$2:$AI$400,Perf_Results!$C$2:$C$400,$A28),""))</f>
+        <v/>
+      </c>
+      <c r="G28" s="20" t="str">
+        <f aca="false">IF($E28=0,"",IFERROR(_xlfn.MAXIFS(Perf_Results!$AS$2:$AS$400,Perf_Results!$C$2:$C$400,$A28),""))</f>
+        <v/>
+      </c>
+      <c r="H28" s="20" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Perf_Results!$Z$2:$Z$400,Perf_Results!$C$2:$C$400,$A28,Perf_Results!$O$2:$O$400,1),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="31" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Perf_Results!$AL$2:$AL$400,Perf_Results!$C$2:$C$400,$A28),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="32" t="str">
+        <f aca="false">IF($E28=0,"",IFERROR(_xlfn.MAXIFS(Perf_Results!$AU$2:$AU$400,Perf_Results!$C$2:$C$400,$A28),""))</f>
+        <v/>
+      </c>
+      <c r="K28" s="33" t="str">
+        <f aca="false">IF($E28=0,"",IFERROR(_xlfn.MINIFS(Perf_Results!$AW$2:$AW$400,Perf_Results!$C$2:$C$400,$A28),""))</f>
+        <v/>
+      </c>
+      <c r="L28" s="34" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Perf_Results!$AR$2:$AR$400,Perf_Results!$C$2:$C$400,$A28),"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="30" t="n">
+        <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A28,Perf_Results!$AX$2:$AX$400,"PASS",Perf_Results!$AY$2:$AY$400,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="N28" s="30" t="n">
+        <f aca="false">COUNTIFS(Quality_Results!$C$2:$C$300,$A28)</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="32" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Quality_Results!$Q$2:$Q$300,Quality_Results!$C$2:$C$300,$A28),"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="31" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Quality_Results!$AF$2:$AF$300,Quality_Results!$C$2:$C$300,$A28),"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>797</v>
+      <c r="A29" s="29" t="str">
+        <f aca="false">IF(Models!A29="","",Models!A29)</f>
+        <v>sea-lion-v3</v>
+      </c>
+      <c r="B29" s="29" t="str">
+        <f aca="false">IF(Models!B29="","",Models!B29)</f>
+        <v>SEA-LION v3 (Gemma-based)</v>
+      </c>
+      <c r="C29" s="29" t="str">
+        <f aca="false">IF(Models!C29="","",Models!C29)</f>
+        <v>AI Singapore</v>
+      </c>
+      <c r="D29" s="29" t="str">
+        <f aca="false">IF(Models!D29="","",Models!D29)</f>
+        <v>Singapore</v>
+      </c>
+      <c r="E29" s="30" t="n">
+        <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A29)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="20" t="str">
+        <f aca="false">IF($E29=0,"",IFERROR(_xlfn.MAXIFS(Perf_Results!$AI$2:$AI$400,Perf_Results!$C$2:$C$400,$A29),""))</f>
+        <v/>
+      </c>
+      <c r="G29" s="20" t="str">
+        <f aca="false">IF($E29=0,"",IFERROR(_xlfn.MAXIFS(Perf_Results!$AS$2:$AS$400,Perf_Results!$C$2:$C$400,$A29),""))</f>
+        <v/>
+      </c>
+      <c r="H29" s="20" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Perf_Results!$Z$2:$Z$400,Perf_Results!$C$2:$C$400,$A29,Perf_Results!$O$2:$O$400,1),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="31" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Perf_Results!$AL$2:$AL$400,Perf_Results!$C$2:$C$400,$A29),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="32" t="str">
+        <f aca="false">IF($E29=0,"",IFERROR(_xlfn.MAXIFS(Perf_Results!$AU$2:$AU$400,Perf_Results!$C$2:$C$400,$A29),""))</f>
+        <v/>
+      </c>
+      <c r="K29" s="33" t="str">
+        <f aca="false">IF($E29=0,"",IFERROR(_xlfn.MINIFS(Perf_Results!$AW$2:$AW$400,Perf_Results!$C$2:$C$400,$A29),""))</f>
+        <v/>
+      </c>
+      <c r="L29" s="34" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Perf_Results!$AR$2:$AR$400,Perf_Results!$C$2:$C$400,$A29),"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="30" t="n">
+        <f aca="false">COUNTIFS(Perf_Results!$C$2:$C$400,$A29,Perf_Results!$AX$2:$AX$400,"PASS",Perf_Results!$AY$2:$AY$400,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="30" t="n">
+        <f aca="false">COUNTIFS(Quality_Results!$C$2:$C$300,$A29)</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="32" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Quality_Results!$Q$2:$Q$300,Quality_Results!$C$2:$C$300,$A29),"")</f>
+        <v/>
+      </c>
+      <c r="P29" s="31" t="str">
+        <f aca="false">IFERROR(AVERAGEIFS(Quality_Results!$AF$2:$AF$300,Quality_Results!$C$2:$C$300,$A29),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -8052,7 +8220,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -8624,7 +8792,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>600</v>
       </c>
@@ -8676,7 +8844,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
         <v>606</v>
       </c>
@@ -8684,7 +8852,7 @@
         <v>607</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>568</v>
@@ -8696,156 +8864,158 @@
         <v>498</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>561</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>4096</v>
+        <v>128000</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>555</v>
+        <v>608</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>609</v>
       </c>
       <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
+      <c r="N15" s="13" t="s">
+        <v>610</v>
+      </c>
       <c r="O15" s="13" t="s">
         <v>66</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>610</v>
+        <v>477</v>
       </c>
       <c r="Q15" s="13" t="s">
+        <v>580</v>
+      </c>
+      <c r="R15" s="14" t="s">
         <v>611</v>
       </c>
-      <c r="R15" s="14" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="B16" s="13" t="s">
         <v>613</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>614</v>
-      </c>
       <c r="C16" s="13" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>616</v>
+        <v>568</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>498</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>561</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>128000</v>
+        <v>4096</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>555</v>
+        <v>614</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="O16" s="13" t="s">
         <v>66</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>477</v>
+        <v>617</v>
       </c>
       <c r="Q16" s="13" t="s">
-        <v>544</v>
-      </c>
-      <c r="R16" s="14"/>
+        <v>618</v>
+      </c>
+      <c r="R16" s="14" t="s">
+        <v>619</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>616</v>
+        <v>568</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>498</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>65536</v>
+        <v>4096</v>
       </c>
       <c r="K17" s="13" t="s">
         <v>555</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M17" s="13"/>
-      <c r="N17" s="13" t="s">
-        <v>622</v>
-      </c>
+      <c r="N17" s="13"/>
       <c r="O17" s="13" t="s">
         <v>66</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>543</v>
+        <v>617</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="R17" s="14" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>538</v>
+        <v>628</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>539</v>
@@ -8854,50 +9024,50 @@
         <v>498</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>355</v>
+        <v>24</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="J18" s="13" t="n">
         <v>128000</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
+      <c r="N18" s="13" t="s">
+        <v>630</v>
+      </c>
       <c r="O18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>543</v>
+        <v>477</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>580</v>
-      </c>
-      <c r="R18" s="14" t="s">
-        <v>628</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="R18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>538</v>
+        <v>628</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>539</v>
@@ -8906,33 +9076,35 @@
         <v>498</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>1000</v>
+        <v>141</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>540</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>128000</v>
+        <v>65536</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>632</v>
+        <v>555</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>633</v>
       </c>
       <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
+      <c r="N19" s="13" t="s">
+        <v>634</v>
+      </c>
       <c r="O19" s="13" t="s">
         <v>66</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>634</v>
+        <v>543</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>580</v>
+        <v>618</v>
       </c>
       <c r="R19" s="14" t="s">
         <v>635</v>
@@ -8958,19 +9130,19 @@
         <v>498</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>456</v>
+        <v>355</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>540</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>1000000</v>
+        <v>128000</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>639</v>
@@ -8981,10 +9153,10 @@
         <v>66</v>
       </c>
       <c r="P20" s="13" t="s">
-        <v>610</v>
+        <v>543</v>
       </c>
       <c r="Q20" s="13" t="s">
-        <v>611</v>
+        <v>580</v>
       </c>
       <c r="R20" s="14" t="s">
         <v>640</v>
@@ -9010,22 +9182,22 @@
         <v>498</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>32768</v>
+        <v>128000</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>555</v>
+        <v>644</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
@@ -9033,25 +9205,27 @@
         <v>66</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>610</v>
+        <v>646</v>
       </c>
       <c r="Q21" s="13" t="s">
-        <v>611</v>
-      </c>
-      <c r="R21" s="14"/>
+        <v>580</v>
+      </c>
+      <c r="R21" s="14" t="s">
+        <v>647</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>648</v>
+        <v>538</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>539</v>
@@ -9060,35 +9234,33 @@
         <v>498</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>32</v>
+        <v>456</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>128000</v>
+        <v>1000000</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>649</v>
+        <v>555</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M22" s="13"/>
-      <c r="N22" s="13" t="s">
-        <v>651</v>
-      </c>
+      <c r="N22" s="13"/>
       <c r="O22" s="13" t="s">
         <v>66</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="Q22" s="13" t="s">
-        <v>580</v>
+        <v>618</v>
       </c>
       <c r="R22" s="14" t="s">
         <v>652</v>
@@ -9105,7 +9277,7 @@
         <v>655</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>656</v>
+        <v>538</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>539</v>
@@ -9114,10 +9286,10 @@
         <v>498</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>561</v>
@@ -9126,38 +9298,36 @@
         <v>32768</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>657</v>
+        <v>555</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="M23" s="13"/>
-      <c r="N23" s="13" t="s">
-        <v>659</v>
-      </c>
+      <c r="N23" s="13"/>
       <c r="O23" s="13" t="s">
         <v>66</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>660</v>
+        <v>617</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="R23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>539</v>
@@ -9166,50 +9336,52 @@
         <v>498</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>665</v>
+        <v>561</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>256000</v>
+        <v>128000</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
+      <c r="N24" s="13" t="s">
+        <v>663</v>
+      </c>
       <c r="O24" s="13" t="s">
         <v>66</v>
       </c>
       <c r="P24" s="13" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="Q24" s="13" t="s">
-        <v>611</v>
+        <v>580</v>
       </c>
       <c r="R24" s="14" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>539</v>
@@ -9218,50 +9390,50 @@
         <v>498</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>561</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>128000</v>
+        <v>32768</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
+      <c r="N25" s="13" t="s">
+        <v>671</v>
+      </c>
       <c r="O25" s="13" t="s">
         <v>66</v>
       </c>
       <c r="P25" s="13" t="s">
-        <v>610</v>
+        <v>672</v>
       </c>
       <c r="Q25" s="13" t="s">
-        <v>611</v>
-      </c>
-      <c r="R25" s="14" t="s">
+        <v>618</v>
+      </c>
+      <c r="R25" s="14"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>673</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>674</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
+      <c r="D26" s="13" t="s">
         <v>676</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>677</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>678</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>679</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>539</v>
@@ -9270,22 +9442,22 @@
         <v>498</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>561</v>
+        <v>677</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>32768</v>
+        <v>256000</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>555</v>
+        <v>678</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="M26" s="13"/>
       <c r="N26" s="13"/>
@@ -9293,27 +9465,27 @@
         <v>66</v>
       </c>
       <c r="P26" s="13" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="Q26" s="13" t="s">
-        <v>580</v>
+        <v>618</v>
       </c>
       <c r="R26" s="14" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
+        <v>681</v>
+      </c>
+      <c r="B27" s="13" t="s">
         <v>682</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="C27" s="13" t="s">
         <v>683</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13" t="s">
         <v>684</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>685</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>539</v>
@@ -9322,19 +9494,19 @@
         <v>498</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>561</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v>8192</v>
+        <v>128000</v>
       </c>
       <c r="K27" s="13" t="s">
-        <v>591</v>
+        <v>685</v>
       </c>
       <c r="L27" s="13" t="s">
         <v>686</v>
@@ -9345,22 +9517,126 @@
         <v>66</v>
       </c>
       <c r="P27" s="13" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="Q27" s="13" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="R27" s="14" t="s">
         <v>687</v>
       </c>
     </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>688</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>689</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>690</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>691</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>32768</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>692</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P28" s="13" t="s">
+        <v>617</v>
+      </c>
+      <c r="Q28" s="13" t="s">
+        <v>580</v>
+      </c>
+      <c r="R28" s="14" t="s">
+        <v>693</v>
+      </c>
+    </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>688</v>
+      <c r="A29" s="13" t="s">
+        <v>694</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>695</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>697</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P29" s="13" t="s">
+        <v>617</v>
+      </c>
+      <c r="Q29" s="13" t="s">
+        <v>618</v>
+      </c>
+      <c r="R29" s="14" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="s">
+        <v>700</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R27"/>
+  <autoFilter ref="A4:R29"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -9394,17 +9670,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>65</v>
@@ -9413,28 +9689,28 @@
         <v>531</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>
@@ -9466,17 +9742,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>369</v>
@@ -9485,7 +9761,7 @@
         <v>58</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9499,7 +9775,7 @@
         <v>233</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9513,12 +9789,12 @@
         <v>242</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>8</v>
@@ -9527,7 +9803,7 @@
         <v>106</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9541,7 +9817,7 @@
         <v>193</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9555,7 +9831,7 @@
         <v>251</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9569,7 +9845,7 @@
         <v>256</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9588,7 +9864,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>0.15</v>
@@ -9597,12 +9873,12 @@
         <v>193</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -9610,92 +9886,92 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">B5/B6</f>
         <v>87500</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="B16" s="19" t="n">
         <f aca="false">B5*B12</f>
         <v>52500</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="B17" s="20" t="n">
         <f aca="false">B9*B10*8760*B8</f>
         <v>87564.96</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="B18" s="19" t="n">
         <f aca="false">B17*B11</f>
         <v>7880.8464</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="B19" s="19" t="n">
         <f aca="false">B15+B16+B18</f>
         <v>147880.8464</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="B20" s="20" t="n">
         <f aca="false">B7*8760*B8</f>
         <v>49056</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9710,7 +9986,7 @@
         <v>233</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -9741,10 +10017,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>65</v>
@@ -9759,7 +10035,7 @@
         <v>101</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>105</v>
@@ -9768,7 +10044,7 @@
         <v>109</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>378</v>
@@ -9801,43 +10077,43 @@
         <v>148</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="X1" s="7" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="Y1" s="7" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="Z1" s="7" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="AA1" s="7" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="AB1" s="7" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="AC1" s="7" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="AD1" s="7" t="s">
         <v>162</v>
       </c>
       <c r="AE1" s="7" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="AF1" s="7" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="AG1" s="7" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="AH1" s="7" t="s">
         <v>169</v>
@@ -9858,10 +10134,10 @@
         <v>192</v>
       </c>
       <c r="AN1" s="7" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="AO1" s="7" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="AP1" s="7" t="s">
         <v>123</v>
@@ -9899,25 +10175,25 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="H2" s="22" t="n">
         <v>2</v>
@@ -9926,7 +10202,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="K2" s="22" t="n">
         <v>2</v>
@@ -9935,10 +10211,10 @@
         <v>32768</v>
       </c>
       <c r="M2" s="22" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="N2" s="22" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="O2" s="22" t="n">
         <v>32</v>
@@ -10058,7 +10334,7 @@
         <v>PASS</v>
       </c>
       <c r="AZ2" s="22" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23638,10 +23914,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>65</v>
@@ -23653,49 +23929,49 @@
         <v>101</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>302</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>490</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>330</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>272</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="U1" s="7" t="s">
         <v>282</v>
@@ -23716,19 +23992,19 @@
         <v>321</v>
       </c>
       <c r="AA1" s="7" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="AB1" s="7" t="s">
         <v>317</v>
       </c>
       <c r="AC1" s="7" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="AD1" s="7" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="AE1" s="7" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="AF1" s="7" t="s">
         <v>314</v>
@@ -23739,31 +24015,31 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="J2" s="22" t="n">
         <v>1000</v>
@@ -23784,7 +24060,7 @@
         <v>42</v>
       </c>
       <c r="P2" s="22" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="Q2" s="22" t="n">
         <v>0.712</v>
@@ -23818,10 +24094,10 @@
         <v>4.9</v>
       </c>
       <c r="AB2" s="22" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="AC2" s="22" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="AD2" s="25" t="n">
         <f aca="false">IFERROR(1.96*R2/SQRT(J2*K2),"")</f>
@@ -23836,7 +24112,7 @@
         <v>0</v>
       </c>
       <c r="AG2" s="22" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
